--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5014" uniqueCount="1564">
   <si>
     <t>Data</t>
   </si>
@@ -6958,6 +6958,9 @@
       <c r="D56" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="E56" s="4" t="s">
+        <v>1562</v>
+      </c>
       <c r="F56" s="4" t="s">
         <v>128</v>
       </c>
@@ -15044,6 +15047,9 @@
       <c r="D444" s="7" t="s">
         <v>733</v>
       </c>
+      <c r="E444" s="4" t="s">
+        <v>1562</v>
+      </c>
       <c r="F444" s="4" t="s">
         <v>734</v>
       </c>
@@ -15061,6 +15067,9 @@
       </c>
       <c r="D445" s="7" t="s">
         <v>727</v>
+      </c>
+      <c r="E445" s="4" t="s">
+        <v>1562</v>
       </c>
       <c r="F445" s="4" t="s">
         <v>736</v>

--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5015" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1573">
   <si>
     <t>Data</t>
   </si>
@@ -4709,6 +4709,33 @@
   </si>
   <si>
     <t>equipe</t>
+  </si>
+  <si>
+    <t>total de ocorrencia abril</t>
+  </si>
+  <si>
+    <t>total de ocorrencia maio</t>
+  </si>
+  <si>
+    <t>total de ocorrencia junho</t>
+  </si>
+  <si>
+    <t>total de ocorrencia capturada abril</t>
+  </si>
+  <si>
+    <t>total de ocorrencia capturada maio</t>
+  </si>
+  <si>
+    <t>total de ocorrencia capturada junho</t>
+  </si>
+  <si>
+    <t>% de ocorrencia capturada abril</t>
+  </si>
+  <si>
+    <t>% de ocorrencia capturada maio</t>
+  </si>
+  <si>
+    <t>% ocorrencia capturada junho</t>
   </si>
 </sst>
 </file>
@@ -4814,7 +4841,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -4874,11 +4901,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4919,9 +4956,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5229,7 +5271,16 @@
     <col min="5" max="5" width="33" style="1" customWidth="1"/>
     <col min="6" max="6" width="78.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="23" style="1" customWidth="1"/>
-    <col min="8" max="17" width="11.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" style="1" customWidth="1"/>
     <col min="18" max="25" width="9.5546875" style="1" customWidth="1"/>
     <col min="26" max="16384" width="14" style="1"/>
   </cols>
@@ -5255,6 +5306,33 @@
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="28" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>1565</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>1567</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>1568</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>1569</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>1570</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>1572</v>
+      </c>
     </row>
     <row r="4" spans="2:22" ht="9.75" customHeight="1">
       <c r="B4" s="3">
@@ -5273,15 +5351,36 @@
         <v>7</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="H4" s="5">
+        <v>2286</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2019</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1877</v>
+      </c>
+      <c r="K4" s="5">
+        <v>273</v>
+      </c>
+      <c r="L4" s="5">
+        <v>472</v>
+      </c>
+      <c r="M4" s="5">
+        <v>257</v>
+      </c>
+      <c r="N4" s="29">
+        <f>K4/H4</f>
+        <v>0.1194225721784777</v>
+      </c>
+      <c r="O4" s="29">
+        <f>L4/I4</f>
+        <v>0.23377909856364537</v>
+      </c>
+      <c r="P4" s="29">
+        <f>M4/J4</f>
+        <v>0.13692061800745872</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>

--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -13,11 +13,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">plan1!$B$3:$G$1010</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5021" uniqueCount="1570">
   <si>
     <t>Data</t>
   </si>
@@ -4711,31 +4712,22 @@
     <t>equipe</t>
   </si>
   <si>
-    <t>total de ocorrencia abril</t>
-  </si>
-  <si>
-    <t>total de ocorrencia maio</t>
-  </si>
-  <si>
-    <t>total de ocorrencia junho</t>
-  </si>
-  <si>
-    <t>total de ocorrencia capturada abril</t>
-  </si>
-  <si>
-    <t>total de ocorrencia capturada maio</t>
-  </si>
-  <si>
-    <t>total de ocorrencia capturada junho</t>
-  </si>
-  <si>
-    <t>% de ocorrencia capturada abril</t>
-  </si>
-  <si>
-    <t>% de ocorrencia capturada maio</t>
-  </si>
-  <si>
-    <t>% ocorrencia capturada junho</t>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAIO</t>
+  </si>
+  <si>
+    <t>JUNHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total de ocorrencia </t>
+  </si>
+  <si>
+    <t>total de ocorrencia capturadas</t>
+  </si>
+  <si>
+    <t>% de ocorrência capturadas</t>
   </si>
 </sst>
 </file>
@@ -4821,7 +4813,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4838,6 +4830,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -4915,7 +4919,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4960,6 +4964,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5271,7 +5283,7 @@
     <col min="5" max="5" width="33" style="1" customWidth="1"/>
     <col min="6" max="6" width="78.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="23" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -5306,33 +5318,22 @@
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="I3" s="30" t="s">
         <v>1564</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="J3" s="30" t="s">
         <v>1565</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="K3" s="30" t="s">
         <v>1566</v>
       </c>
-      <c r="K3" s="28" t="s">
-        <v>1567</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>1568</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>1569</v>
-      </c>
-      <c r="N3" s="28" t="s">
-        <v>1570</v>
-      </c>
-      <c r="O3" s="28" t="s">
-        <v>1571</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>1572</v>
-      </c>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="32"/>
     </row>
     <row r="4" spans="2:22" ht="9.75" customHeight="1">
       <c r="B4" s="3">
@@ -5351,39 +5352,25 @@
         <v>7</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="5">
+      <c r="H4" s="28" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I4" s="5">
         <v>2286</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>2019</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>1877</v>
       </c>
-      <c r="K4" s="5">
-        <v>273</v>
-      </c>
-      <c r="L4" s="5">
-        <v>472</v>
-      </c>
-      <c r="M4" s="5">
-        <v>257</v>
-      </c>
-      <c r="N4" s="29">
-        <f>K4/H4</f>
-        <v>0.1194225721784777</v>
-      </c>
-      <c r="O4" s="29">
-        <f>L4/I4</f>
-        <v>0.23377909856364537</v>
-      </c>
-      <c r="P4" s="29">
-        <f>M4/J4</f>
-        <v>0.13692061800745872</v>
-      </c>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="33"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
@@ -5406,18 +5393,26 @@
         <v>10</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="H5" s="28" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I5" s="5">
+        <v>273</v>
+      </c>
+      <c r="J5" s="5">
+        <v>472</v>
+      </c>
+      <c r="K5" s="5">
+        <v>257</v>
+      </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
@@ -5441,25 +5436,36 @@
       <c r="G6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="H6" s="28" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I6" s="29">
+        <f>I5/I4</f>
+        <v>0.1194225721784777</v>
+      </c>
+      <c r="J6" s="29">
+        <f>J5/J4</f>
+        <v>0.23377909856364537</v>
+      </c>
+      <c r="K6" s="29">
+        <f>K5/K4</f>
+        <v>0.13692061800745872</v>
+      </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
     </row>
     <row r="7" spans="2:22" ht="9.75" customHeight="1">
       <c r="B7" s="6">
-        <f t="shared" ref="B7:B8" si="0">B6</f>
+        <f>B6</f>
         <v>46115</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -5493,7 +5499,7 @@
     </row>
     <row r="8" spans="2:22" ht="9.75" customHeight="1">
       <c r="B8" s="6">
-        <f t="shared" si="0"/>
+        <f>B7</f>
         <v>46115</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -5562,7 +5568,7 @@
     </row>
     <row r="10" spans="2:22" ht="9.75" customHeight="1">
       <c r="B10" s="6">
-        <f t="shared" ref="B10:B16" si="1">B9</f>
+        <f t="shared" ref="B10:B16" si="0">B9</f>
         <v>46116</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -5598,7 +5604,7 @@
     </row>
     <row r="11" spans="2:22" ht="9.75" customHeight="1">
       <c r="B11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -5634,7 +5640,7 @@
     </row>
     <row r="12" spans="2:22" ht="9.75" customHeight="1">
       <c r="B12" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -5670,7 +5676,7 @@
     </row>
     <row r="13" spans="2:22" ht="9.75" customHeight="1">
       <c r="B13" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -5706,7 +5712,7 @@
     </row>
     <row r="14" spans="2:22" ht="9.75" customHeight="1">
       <c r="B14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5742,7 +5748,7 @@
     </row>
     <row r="15" spans="2:22" ht="9.75" customHeight="1">
       <c r="B15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -5778,7 +5784,7 @@
     </row>
     <row r="16" spans="2:22" ht="9.75" customHeight="1">
       <c r="B16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>46116</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -5847,7 +5853,7 @@
     </row>
     <row r="18" spans="2:22" ht="9.75" customHeight="1">
       <c r="B18" s="6">
-        <f t="shared" ref="B18:B20" si="2">B17</f>
+        <f>B17</f>
         <v>46117</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5883,7 +5889,7 @@
     </row>
     <row r="19" spans="2:22" ht="9.75" customHeight="1">
       <c r="B19" s="6">
-        <f t="shared" si="2"/>
+        <f>B18</f>
         <v>46117</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -5919,7 +5925,7 @@
     </row>
     <row r="20" spans="2:22" ht="9.75" customHeight="1">
       <c r="B20" s="6">
-        <f t="shared" si="2"/>
+        <f>B19</f>
         <v>46117</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5990,7 +5996,7 @@
     </row>
     <row r="22" spans="2:22" ht="9.75" customHeight="1">
       <c r="B22" s="6">
-        <f t="shared" ref="B22:B33" si="3">B21</f>
+        <f t="shared" ref="B22:B33" si="1">B21</f>
         <v>46118</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -6026,7 +6032,7 @@
     </row>
     <row r="23" spans="2:22" ht="9.75" customHeight="1">
       <c r="B23" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -6062,7 +6068,7 @@
     </row>
     <row r="24" spans="2:22" ht="9.75" customHeight="1">
       <c r="B24" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -6098,7 +6104,7 @@
     </row>
     <row r="25" spans="2:22" ht="9.75" customHeight="1">
       <c r="B25" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -6134,7 +6140,7 @@
     </row>
     <row r="26" spans="2:22" ht="9.75" customHeight="1">
       <c r="B26" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -6170,7 +6176,7 @@
     </row>
     <row r="27" spans="2:22" ht="9.75" customHeight="1">
       <c r="B27" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -6206,7 +6212,7 @@
     </row>
     <row r="28" spans="2:22" ht="9.75" customHeight="1">
       <c r="B28" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -6242,7 +6248,7 @@
     </row>
     <row r="29" spans="2:22" ht="9.75" customHeight="1">
       <c r="B29" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -6278,7 +6284,7 @@
     </row>
     <row r="30" spans="2:22" ht="9.75" customHeight="1">
       <c r="B30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -6314,7 +6320,7 @@
     </row>
     <row r="31" spans="2:22" ht="9.75" customHeight="1">
       <c r="B31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -6350,7 +6356,7 @@
     </row>
     <row r="32" spans="2:22" ht="9.75" customHeight="1">
       <c r="B32" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -6386,7 +6392,7 @@
     </row>
     <row r="33" spans="2:22" ht="9.75" customHeight="1">
       <c r="B33" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -6457,7 +6463,7 @@
     </row>
     <row r="35" spans="2:22" ht="9.75" customHeight="1">
       <c r="B35" s="6">
-        <f t="shared" ref="B35:B41" si="4">B34</f>
+        <f t="shared" ref="B35:B41" si="2">B34</f>
         <v>46119</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -6493,7 +6499,7 @@
     </row>
     <row r="36" spans="2:22" ht="9.75" customHeight="1">
       <c r="B36" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -6529,7 +6535,7 @@
     </row>
     <row r="37" spans="2:22" ht="9.75" customHeight="1">
       <c r="B37" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -6565,7 +6571,7 @@
     </row>
     <row r="38" spans="2:22" ht="9.75" customHeight="1">
       <c r="B38" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -6601,7 +6607,7 @@
     </row>
     <row r="39" spans="2:22" ht="9.75" customHeight="1">
       <c r="B39" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -6637,7 +6643,7 @@
     </row>
     <row r="40" spans="2:22" ht="9.75" customHeight="1">
       <c r="B40" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -6673,7 +6679,7 @@
     </row>
     <row r="41" spans="2:22" ht="9.75" customHeight="1">
       <c r="B41" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>46119</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -6742,7 +6748,7 @@
     </row>
     <row r="43" spans="2:22" ht="9.75" customHeight="1">
       <c r="B43" s="6">
-        <f t="shared" ref="B43:B53" si="5">B42</f>
+        <f t="shared" ref="B43:B53" si="3">B42</f>
         <v>46120</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -6778,7 +6784,7 @@
     </row>
     <row r="44" spans="2:22" ht="9.75" customHeight="1">
       <c r="B44" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -6814,7 +6820,7 @@
     </row>
     <row r="45" spans="2:22" ht="9.75" customHeight="1">
       <c r="B45" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -6850,7 +6856,7 @@
     </row>
     <row r="46" spans="2:22" ht="9.75" customHeight="1">
       <c r="B46" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -6871,7 +6877,7 @@
     </row>
     <row r="47" spans="2:22" ht="9.75" customHeight="1">
       <c r="B47" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -6892,7 +6898,7 @@
     </row>
     <row r="48" spans="2:22" ht="9.75" customHeight="1">
       <c r="B48" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -6913,7 +6919,7 @@
     </row>
     <row r="49" spans="2:7" ht="9.75" customHeight="1">
       <c r="B49" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -6934,7 +6940,7 @@
     </row>
     <row r="50" spans="2:7" ht="9.75" customHeight="1">
       <c r="B50" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C50" s="11"/>
@@ -6947,7 +6953,7 @@
     </row>
     <row r="51" spans="2:7" ht="9.75" customHeight="1">
       <c r="B51" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -6968,7 +6974,7 @@
     </row>
     <row r="52" spans="2:7" ht="9.75" customHeight="1">
       <c r="B52" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -6989,7 +6995,7 @@
     </row>
     <row r="53" spans="2:7" ht="9.75" customHeight="1">
       <c r="B53" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>46120</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -7050,7 +7056,7 @@
     </row>
     <row r="56" spans="2:7" ht="9.75" customHeight="1">
       <c r="B56" s="6">
-        <f t="shared" ref="B56" si="6">B55</f>
+        <f>B55</f>
         <v>46122</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -7091,7 +7097,7 @@
     </row>
     <row r="58" spans="2:7" ht="9.75" customHeight="1">
       <c r="B58" s="6">
-        <f t="shared" ref="B58:B64" si="7">B57</f>
+        <f t="shared" ref="B58:B64" si="4">B57</f>
         <v>46123</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -7112,7 +7118,7 @@
     </row>
     <row r="59" spans="2:7" ht="9.75" customHeight="1">
       <c r="B59" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -7133,7 +7139,7 @@
     </row>
     <row r="60" spans="2:7" ht="9.75" customHeight="1">
       <c r="B60" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -7154,7 +7160,7 @@
     </row>
     <row r="61" spans="2:7" ht="9.75" customHeight="1">
       <c r="B61" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -7175,7 +7181,7 @@
     </row>
     <row r="62" spans="2:7" ht="9.75" customHeight="1">
       <c r="B62" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -7196,7 +7202,7 @@
     </row>
     <row r="63" spans="2:7" ht="9.75" customHeight="1">
       <c r="B63" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -7217,7 +7223,7 @@
     </row>
     <row r="64" spans="2:7" ht="9.75" customHeight="1">
       <c r="B64" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46123</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -7256,7 +7262,7 @@
     </row>
     <row r="66" spans="2:7" ht="9.75" customHeight="1">
       <c r="B66" s="6">
-        <f t="shared" ref="B66:B76" si="8">B65</f>
+        <f t="shared" ref="B66:B76" si="5">B65</f>
         <v>46124</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -7277,7 +7283,7 @@
     </row>
     <row r="67" spans="2:7" ht="9.75" customHeight="1">
       <c r="B67" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -7298,7 +7304,7 @@
     </row>
     <row r="68" spans="2:7" ht="9.75" customHeight="1">
       <c r="B68" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -7319,7 +7325,7 @@
     </row>
     <row r="69" spans="2:7" ht="9.75" customHeight="1">
       <c r="B69" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -7340,7 +7346,7 @@
     </row>
     <row r="70" spans="2:7" ht="9.75" customHeight="1">
       <c r="B70" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -7361,7 +7367,7 @@
     </row>
     <row r="71" spans="2:7" ht="9.75" customHeight="1">
       <c r="B71" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -7382,7 +7388,7 @@
     </row>
     <row r="72" spans="2:7" ht="9.75" customHeight="1">
       <c r="B72" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C72" s="4" t="s">
@@ -7403,7 +7409,7 @@
     </row>
     <row r="73" spans="2:7" ht="9.75" customHeight="1">
       <c r="B73" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -7424,7 +7430,7 @@
     </row>
     <row r="74" spans="2:7" ht="9.75" customHeight="1">
       <c r="B74" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -7445,7 +7451,7 @@
     </row>
     <row r="75" spans="2:7" ht="9.75" customHeight="1">
       <c r="B75" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -7466,7 +7472,7 @@
     </row>
     <row r="76" spans="2:7" ht="9.75" customHeight="1">
       <c r="B76" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>46124</v>
       </c>
       <c r="C76" s="4" t="s">
@@ -7523,7 +7529,7 @@
     </row>
     <row r="79" spans="2:7" ht="9.75" customHeight="1">
       <c r="B79" s="6">
-        <f t="shared" ref="B79:B96" si="9">B78</f>
+        <f t="shared" ref="B79:B96" si="6">B78</f>
         <v>46128</v>
       </c>
       <c r="C79" s="7" t="s">
@@ -7544,7 +7550,7 @@
     </row>
     <row r="80" spans="2:7" ht="9.75" customHeight="1">
       <c r="B80" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -7565,7 +7571,7 @@
     </row>
     <row r="81" spans="2:7" ht="9.75" customHeight="1">
       <c r="B81" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -7586,7 +7592,7 @@
     </row>
     <row r="82" spans="2:7" ht="9.75" customHeight="1">
       <c r="B82" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -7607,7 +7613,7 @@
     </row>
     <row r="83" spans="2:7" ht="9.75" customHeight="1">
       <c r="B83" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -7628,7 +7634,7 @@
     </row>
     <row r="84" spans="2:7" ht="9.75" customHeight="1">
       <c r="B84" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -7649,7 +7655,7 @@
     </row>
     <row r="85" spans="2:7" ht="9.75" customHeight="1">
       <c r="B85" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -7670,7 +7676,7 @@
     </row>
     <row r="86" spans="2:7" ht="9.75" customHeight="1">
       <c r="B86" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -7691,7 +7697,7 @@
     </row>
     <row r="87" spans="2:7" ht="9.75" customHeight="1">
       <c r="B87" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -7712,7 +7718,7 @@
     </row>
     <row r="88" spans="2:7" ht="9.75" customHeight="1">
       <c r="B88" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -7733,7 +7739,7 @@
     </row>
     <row r="89" spans="2:7" ht="9.75" customHeight="1">
       <c r="B89" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -7754,7 +7760,7 @@
     </row>
     <row r="90" spans="2:7" ht="9.75" customHeight="1">
       <c r="B90" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -7775,7 +7781,7 @@
     </row>
     <row r="91" spans="2:7" ht="9.75" customHeight="1">
       <c r="B91" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -7796,7 +7802,7 @@
     </row>
     <row r="92" spans="2:7" ht="9.75" customHeight="1">
       <c r="B92" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -7817,7 +7823,7 @@
     </row>
     <row r="93" spans="2:7" ht="9.75" customHeight="1">
       <c r="B93" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C93" s="4" t="s">
@@ -7838,7 +7844,7 @@
     </row>
     <row r="94" spans="2:7" ht="9.75" customHeight="1">
       <c r="B94" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -7859,7 +7865,7 @@
     </row>
     <row r="95" spans="2:7" ht="9.75" customHeight="1">
       <c r="B95" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -7880,7 +7886,7 @@
     </row>
     <row r="96" spans="2:7" ht="9.75" customHeight="1">
       <c r="B96" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -7921,7 +7927,7 @@
     </row>
     <row r="98" spans="2:7" ht="9.75" customHeight="1">
       <c r="B98" s="6">
-        <f t="shared" ref="B98:B114" si="10">B97</f>
+        <f t="shared" ref="B98:B114" si="7">B97</f>
         <v>46129</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -7942,7 +7948,7 @@
     </row>
     <row r="99" spans="2:7" ht="9.75" customHeight="1">
       <c r="B99" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -7963,7 +7969,7 @@
     </row>
     <row r="100" spans="2:7" ht="9.75" customHeight="1">
       <c r="B100" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C100" s="4" t="s">
@@ -7984,7 +7990,7 @@
     </row>
     <row r="101" spans="2:7" ht="15.75" customHeight="1">
       <c r="B101" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -8005,7 +8011,7 @@
     </row>
     <row r="102" spans="2:7" ht="15.75" customHeight="1">
       <c r="B102" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -8026,7 +8032,7 @@
     </row>
     <row r="103" spans="2:7" ht="15.75" customHeight="1">
       <c r="B103" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -8047,7 +8053,7 @@
     </row>
     <row r="104" spans="2:7" ht="15.75" customHeight="1">
       <c r="B104" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -8068,7 +8074,7 @@
     </row>
     <row r="105" spans="2:7" ht="15.75" customHeight="1">
       <c r="B105" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -8089,7 +8095,7 @@
     </row>
     <row r="106" spans="2:7" ht="15.75" customHeight="1">
       <c r="B106" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C106" s="4" t="s">
@@ -8110,7 +8116,7 @@
     </row>
     <row r="107" spans="2:7" ht="15.75" customHeight="1">
       <c r="B107" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -8131,7 +8137,7 @@
     </row>
     <row r="108" spans="2:7" ht="15.75" customHeight="1">
       <c r="B108" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -8152,7 +8158,7 @@
     </row>
     <row r="109" spans="2:7" ht="15.75" customHeight="1">
       <c r="B109" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C109" s="4" t="s">
@@ -8173,7 +8179,7 @@
     </row>
     <row r="110" spans="2:7" ht="15.75" customHeight="1">
       <c r="B110" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C110" s="4" t="s">
@@ -8194,7 +8200,7 @@
     </row>
     <row r="111" spans="2:7" ht="15.75" customHeight="1">
       <c r="B111" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -8215,7 +8221,7 @@
     </row>
     <row r="112" spans="2:7" ht="15.75" customHeight="1">
       <c r="B112" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -8236,7 +8242,7 @@
     </row>
     <row r="113" spans="2:7" ht="15.75" customHeight="1">
       <c r="B113" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -8257,7 +8263,7 @@
     </row>
     <row r="114" spans="2:7" ht="15.75" customHeight="1">
       <c r="B114" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>46129</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -8298,7 +8304,7 @@
     </row>
     <row r="116" spans="2:7" ht="15.75" customHeight="1">
       <c r="B116" s="6">
-        <f t="shared" ref="B116:B118" si="11">B115</f>
+        <f>B115</f>
         <v>46130</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -8319,7 +8325,7 @@
     </row>
     <row r="117" spans="2:7" ht="15.75" customHeight="1">
       <c r="B117" s="6">
-        <f t="shared" si="11"/>
+        <f>B116</f>
         <v>46130</v>
       </c>
       <c r="C117" s="4" t="s">
@@ -8340,7 +8346,7 @@
     </row>
     <row r="118" spans="2:7" ht="15.75" customHeight="1">
       <c r="B118" s="6">
-        <f t="shared" si="11"/>
+        <f>B117</f>
         <v>46130</v>
       </c>
       <c r="C118" s="4" t="s">
@@ -8381,7 +8387,7 @@
     </row>
     <row r="120" spans="2:7" ht="15.75" customHeight="1">
       <c r="B120" s="6">
-        <f t="shared" ref="B120:B129" si="12">B119</f>
+        <f t="shared" ref="B120:B129" si="8">B119</f>
         <v>46131</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -8402,7 +8408,7 @@
     </row>
     <row r="121" spans="2:7" ht="15.75" customHeight="1">
       <c r="B121" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -8423,7 +8429,7 @@
     </row>
     <row r="122" spans="2:7" ht="15.75" customHeight="1">
       <c r="B122" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -8444,7 +8450,7 @@
     </row>
     <row r="123" spans="2:7" ht="15.75" customHeight="1">
       <c r="B123" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C123" s="4" t="s">
@@ -8465,7 +8471,7 @@
     </row>
     <row r="124" spans="2:7" ht="15.75" customHeight="1">
       <c r="B124" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -8486,7 +8492,7 @@
     </row>
     <row r="125" spans="2:7" ht="15.75" customHeight="1">
       <c r="B125" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C125" s="4" t="s">
@@ -8507,7 +8513,7 @@
     </row>
     <row r="126" spans="2:7" ht="15.75" customHeight="1">
       <c r="B126" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C126" s="4" t="s">
@@ -8528,7 +8534,7 @@
     </row>
     <row r="127" spans="2:7" ht="15.75" customHeight="1">
       <c r="B127" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -8549,7 +8555,7 @@
     </row>
     <row r="128" spans="2:7" ht="15.75" customHeight="1">
       <c r="B128" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C128" s="4" t="s">
@@ -8570,7 +8576,7 @@
     </row>
     <row r="129" spans="2:7" ht="15.75" customHeight="1">
       <c r="B129" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>46131</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -8611,7 +8617,7 @@
     </row>
     <row r="131" spans="2:7" ht="15.75" customHeight="1">
       <c r="B131" s="6">
-        <f t="shared" ref="B131:B141" si="13">B130</f>
+        <f t="shared" ref="B131:B141" si="9">B130</f>
         <v>46132</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -8632,7 +8638,7 @@
     </row>
     <row r="132" spans="2:7" ht="15.75" customHeight="1">
       <c r="B132" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -8653,7 +8659,7 @@
     </row>
     <row r="133" spans="2:7" ht="15.75" customHeight="1">
       <c r="B133" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -8674,7 +8680,7 @@
     </row>
     <row r="134" spans="2:7" ht="15.75" customHeight="1">
       <c r="B134" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C134" s="4" t="s">
@@ -8695,7 +8701,7 @@
     </row>
     <row r="135" spans="2:7" ht="15.75" customHeight="1">
       <c r="B135" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C135" s="4" t="s">
@@ -8716,7 +8722,7 @@
     </row>
     <row r="136" spans="2:7" ht="15.75" customHeight="1">
       <c r="B136" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -8737,7 +8743,7 @@
     </row>
     <row r="137" spans="2:7" ht="15.75" customHeight="1">
       <c r="B137" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -8758,7 +8764,7 @@
     </row>
     <row r="138" spans="2:7" ht="15.75" customHeight="1">
       <c r="B138" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -8775,7 +8781,7 @@
     </row>
     <row r="139" spans="2:7" ht="15.75" customHeight="1">
       <c r="B139" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -8796,7 +8802,7 @@
     </row>
     <row r="140" spans="2:7" ht="15.75" customHeight="1">
       <c r="B140" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -8815,7 +8821,7 @@
     </row>
     <row r="141" spans="2:7" ht="15.75" customHeight="1">
       <c r="B141" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>46132</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -8856,7 +8862,7 @@
     </row>
     <row r="143" spans="2:7" ht="15.75" customHeight="1">
       <c r="B143" s="6">
-        <f t="shared" ref="B143:B148" si="14">B142</f>
+        <f t="shared" ref="B143:B148" si="10">B142</f>
         <v>46133</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -8877,7 +8883,7 @@
     </row>
     <row r="144" spans="2:7" ht="15.75" customHeight="1">
       <c r="B144" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>46133</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -8898,7 +8904,7 @@
     </row>
     <row r="145" spans="2:7" ht="15.75" customHeight="1">
       <c r="B145" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>46133</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -8919,7 +8925,7 @@
     </row>
     <row r="146" spans="2:7" ht="15.75" customHeight="1">
       <c r="B146" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>46133</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -8940,7 +8946,7 @@
     </row>
     <row r="147" spans="2:7" ht="15.75" customHeight="1">
       <c r="B147" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>46133</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -8961,7 +8967,7 @@
     </row>
     <row r="148" spans="2:7" ht="15.75" customHeight="1">
       <c r="B148" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>46133</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -9002,7 +9008,7 @@
     </row>
     <row r="150" spans="2:7" ht="15.75" customHeight="1">
       <c r="B150" s="6">
-        <f t="shared" ref="B150:B163" si="15">B149</f>
+        <f t="shared" ref="B150:B163" si="11">B149</f>
         <v>46134</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -9023,7 +9029,7 @@
     </row>
     <row r="151" spans="2:7" ht="15.75" customHeight="1">
       <c r="B151" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -9044,7 +9050,7 @@
     </row>
     <row r="152" spans="2:7" ht="15.75" customHeight="1">
       <c r="B152" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -9065,7 +9071,7 @@
     </row>
     <row r="153" spans="2:7" ht="15.75" customHeight="1">
       <c r="B153" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -9086,7 +9092,7 @@
     </row>
     <row r="154" spans="2:7" ht="15.75" customHeight="1">
       <c r="B154" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -9107,7 +9113,7 @@
     </row>
     <row r="155" spans="2:7" ht="15.75" customHeight="1">
       <c r="B155" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -9128,7 +9134,7 @@
     </row>
     <row r="156" spans="2:7" ht="15.75" customHeight="1">
       <c r="B156" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -9149,7 +9155,7 @@
     </row>
     <row r="157" spans="2:7" ht="15.75" customHeight="1">
       <c r="B157" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -9170,7 +9176,7 @@
     </row>
     <row r="158" spans="2:7" ht="15.75" customHeight="1">
       <c r="B158" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -9191,7 +9197,7 @@
     </row>
     <row r="159" spans="2:7" ht="15.75" customHeight="1">
       <c r="B159" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -9212,7 +9218,7 @@
     </row>
     <row r="160" spans="2:7" ht="15.75" customHeight="1">
       <c r="B160" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -9233,7 +9239,7 @@
     </row>
     <row r="161" spans="2:7" ht="15.75" customHeight="1">
       <c r="B161" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -9254,7 +9260,7 @@
     </row>
     <row r="162" spans="2:7" ht="15.75" customHeight="1">
       <c r="B162" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -9275,7 +9281,7 @@
     </row>
     <row r="163" spans="2:7" ht="15.75" customHeight="1">
       <c r="B163" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46134</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -9316,7 +9322,7 @@
     </row>
     <row r="165" spans="2:7" ht="15.75" customHeight="1">
       <c r="B165" s="6">
-        <f t="shared" ref="B165:B186" si="16">B164</f>
+        <f t="shared" ref="B165:B186" si="12">B164</f>
         <v>46135</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -9337,7 +9343,7 @@
     </row>
     <row r="166" spans="2:7" ht="15.75" customHeight="1">
       <c r="B166" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -9358,7 +9364,7 @@
     </row>
     <row r="167" spans="2:7" ht="15.75" customHeight="1">
       <c r="B167" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C167" s="7" t="s">
@@ -9379,7 +9385,7 @@
     </row>
     <row r="168" spans="2:7" ht="15.75" customHeight="1">
       <c r="B168" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C168" s="7" t="s">
@@ -9400,7 +9406,7 @@
     </row>
     <row r="169" spans="2:7" ht="15.75" customHeight="1">
       <c r="B169" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -9421,7 +9427,7 @@
     </row>
     <row r="170" spans="2:7" ht="15.75" customHeight="1">
       <c r="B170" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -9442,7 +9448,7 @@
     </row>
     <row r="171" spans="2:7" ht="15.75" customHeight="1">
       <c r="B171" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -9463,7 +9469,7 @@
     </row>
     <row r="172" spans="2:7" ht="15.75" customHeight="1">
       <c r="B172" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -9484,7 +9490,7 @@
     </row>
     <row r="173" spans="2:7" ht="15.75" customHeight="1">
       <c r="B173" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -9505,7 +9511,7 @@
     </row>
     <row r="174" spans="2:7" ht="15.75" customHeight="1">
       <c r="B174" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -9526,7 +9532,7 @@
     </row>
     <row r="175" spans="2:7" ht="15.75" customHeight="1">
       <c r="B175" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -9547,7 +9553,7 @@
     </row>
     <row r="176" spans="2:7" ht="15.75" customHeight="1">
       <c r="B176" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C176" s="4" t="s">
@@ -9568,7 +9574,7 @@
     </row>
     <row r="177" spans="2:7" ht="15.75" customHeight="1">
       <c r="B177" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -9589,7 +9595,7 @@
     </row>
     <row r="178" spans="2:7" ht="15.75" customHeight="1">
       <c r="B178" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -9610,7 +9616,7 @@
     </row>
     <row r="179" spans="2:7" ht="15.75" customHeight="1">
       <c r="B179" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -9631,7 +9637,7 @@
     </row>
     <row r="180" spans="2:7" ht="15.75" customHeight="1">
       <c r="B180" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -9652,7 +9658,7 @@
     </row>
     <row r="181" spans="2:7" ht="15.75" customHeight="1">
       <c r="B181" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -9673,7 +9679,7 @@
     </row>
     <row r="182" spans="2:7" ht="15.75" customHeight="1">
       <c r="B182" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -9694,7 +9700,7 @@
     </row>
     <row r="183" spans="2:7" ht="15.75" customHeight="1">
       <c r="B183" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -9715,7 +9721,7 @@
     </row>
     <row r="184" spans="2:7" ht="15.75" customHeight="1">
       <c r="B184" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -9736,7 +9742,7 @@
     </row>
     <row r="185" spans="2:7" ht="15.75" customHeight="1">
       <c r="B185" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -9757,7 +9763,7 @@
     </row>
     <row r="186" spans="2:7" ht="15.75" customHeight="1">
       <c r="B186" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>46135</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -9798,7 +9804,7 @@
     </row>
     <row r="188" spans="2:7" ht="15.75" customHeight="1">
       <c r="B188" s="6">
-        <f t="shared" ref="B188:B194" si="17">B187</f>
+        <f t="shared" ref="B188:B194" si="13">B187</f>
         <v>46136</v>
       </c>
       <c r="C188" s="7" t="s">
@@ -9819,7 +9825,7 @@
     </row>
     <row r="189" spans="2:7" ht="15.75" customHeight="1">
       <c r="B189" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -9840,7 +9846,7 @@
     </row>
     <row r="190" spans="2:7" ht="15.75" customHeight="1">
       <c r="B190" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C190" s="4" t="s">
@@ -9861,7 +9867,7 @@
     </row>
     <row r="191" spans="2:7" ht="15.75" customHeight="1">
       <c r="B191" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C191" s="7" t="s">
@@ -9882,7 +9888,7 @@
     </row>
     <row r="192" spans="2:7" ht="15.75" customHeight="1">
       <c r="B192" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C192" s="7" t="s">
@@ -9903,7 +9909,7 @@
     </row>
     <row r="193" spans="2:7" ht="15.75" customHeight="1">
       <c r="B193" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C193" s="4" t="s">
@@ -9924,7 +9930,7 @@
     </row>
     <row r="194" spans="2:7" ht="15.75" customHeight="1">
       <c r="B194" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>46136</v>
       </c>
       <c r="C194" s="10" t="s">
@@ -9963,7 +9969,7 @@
     </row>
     <row r="196" spans="2:7" ht="15.75" customHeight="1">
       <c r="B196" s="6">
-        <f t="shared" ref="B196:B208" si="18">B195</f>
+        <f t="shared" ref="B196:B208" si="14">B195</f>
         <v>46137</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -9984,7 +9990,7 @@
     </row>
     <row r="197" spans="2:7" ht="15.75" customHeight="1">
       <c r="B197" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C197" s="4" t="s">
@@ -10005,7 +10011,7 @@
     </row>
     <row r="198" spans="2:7" ht="15.75" customHeight="1">
       <c r="B198" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C198" s="4" t="s">
@@ -10026,7 +10032,7 @@
     </row>
     <row r="199" spans="2:7" ht="15.75" customHeight="1">
       <c r="B199" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C199" s="7" t="s">
@@ -10047,7 +10053,7 @@
     </row>
     <row r="200" spans="2:7" ht="15.75" customHeight="1">
       <c r="B200" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C200" s="7" t="s">
@@ -10068,7 +10074,7 @@
     </row>
     <row r="201" spans="2:7" ht="15.75" customHeight="1">
       <c r="B201" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C201" s="7" t="s">
@@ -10089,7 +10095,7 @@
     </row>
     <row r="202" spans="2:7" ht="15.75" customHeight="1">
       <c r="B202" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -10110,7 +10116,7 @@
     </row>
     <row r="203" spans="2:7" ht="15.75" customHeight="1">
       <c r="B203" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -10131,7 +10137,7 @@
     </row>
     <row r="204" spans="2:7" ht="15.75" customHeight="1">
       <c r="B204" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -10152,7 +10158,7 @@
     </row>
     <row r="205" spans="2:7" ht="15.75" customHeight="1">
       <c r="B205" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C205" s="7" t="s">
@@ -10173,7 +10179,7 @@
     </row>
     <row r="206" spans="2:7" ht="15.75" customHeight="1">
       <c r="B206" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C206" s="7" t="s">
@@ -10194,7 +10200,7 @@
     </row>
     <row r="207" spans="2:7" ht="15.75" customHeight="1">
       <c r="B207" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C207" s="7" t="s">
@@ -10215,7 +10221,7 @@
     </row>
     <row r="208" spans="2:7" ht="15.75" customHeight="1">
       <c r="B208" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>46137</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -10256,7 +10262,7 @@
     </row>
     <row r="210" spans="2:7" ht="15.75" customHeight="1">
       <c r="B210" s="6">
-        <f t="shared" ref="B210:B227" si="19">B209</f>
+        <f t="shared" ref="B210:B227" si="15">B209</f>
         <v>46138</v>
       </c>
       <c r="C210" s="7" t="s">
@@ -10277,7 +10283,7 @@
     </row>
     <row r="211" spans="2:7" ht="15.75" customHeight="1">
       <c r="B211" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -10298,7 +10304,7 @@
     </row>
     <row r="212" spans="2:7" ht="15.75" customHeight="1">
       <c r="B212" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C212" s="4" t="s">
@@ -10319,7 +10325,7 @@
     </row>
     <row r="213" spans="2:7" ht="15.75" customHeight="1">
       <c r="B213" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -10340,7 +10346,7 @@
     </row>
     <row r="214" spans="2:7" ht="15.75" customHeight="1">
       <c r="B214" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -10361,7 +10367,7 @@
     </row>
     <row r="215" spans="2:7" ht="15.75" customHeight="1">
       <c r="B215" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -10382,7 +10388,7 @@
     </row>
     <row r="216" spans="2:7" ht="15.75" customHeight="1">
       <c r="B216" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -10403,7 +10409,7 @@
     </row>
     <row r="217" spans="2:7" ht="15.75" customHeight="1">
       <c r="B217" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C217" s="4" t="s">
@@ -10424,7 +10430,7 @@
     </row>
     <row r="218" spans="2:7" ht="15.75" customHeight="1">
       <c r="B218" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -10445,7 +10451,7 @@
     </row>
     <row r="219" spans="2:7" ht="15.75" customHeight="1">
       <c r="B219" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -10466,7 +10472,7 @@
     </row>
     <row r="220" spans="2:7" ht="15.75" customHeight="1">
       <c r="B220" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -10487,7 +10493,7 @@
     </row>
     <row r="221" spans="2:7" ht="15.75" customHeight="1">
       <c r="B221" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C221" s="4" t="s">
@@ -10508,7 +10514,7 @@
     </row>
     <row r="222" spans="2:7" ht="15.75" customHeight="1">
       <c r="B222" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -10529,7 +10535,7 @@
     </row>
     <row r="223" spans="2:7" ht="15.75" customHeight="1">
       <c r="B223" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C223" s="4" t="s">
@@ -10550,7 +10556,7 @@
     </row>
     <row r="224" spans="2:7" ht="15.75" customHeight="1">
       <c r="B224" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -10571,7 +10577,7 @@
     </row>
     <row r="225" spans="2:7" ht="15.75" customHeight="1">
       <c r="B225" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C225" s="4" t="s">
@@ -10592,7 +10598,7 @@
     </row>
     <row r="226" spans="2:7" ht="15.75" customHeight="1">
       <c r="B226" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C226" s="4" t="s">
@@ -10613,7 +10619,7 @@
     </row>
     <row r="227" spans="2:7" ht="15.75" customHeight="1">
       <c r="B227" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>46138</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -10654,7 +10660,7 @@
     </row>
     <row r="229" spans="2:7" ht="15.75" customHeight="1">
       <c r="B229" s="6">
-        <f t="shared" ref="B229:B233" si="20">B228</f>
+        <f>B228</f>
         <v>46139</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -10675,7 +10681,7 @@
     </row>
     <row r="230" spans="2:7" ht="15.75" customHeight="1">
       <c r="B230" s="6">
-        <f t="shared" si="20"/>
+        <f>B229</f>
         <v>46139</v>
       </c>
       <c r="C230" s="4" t="s">
@@ -10696,7 +10702,7 @@
     </row>
     <row r="231" spans="2:7" ht="15.75" customHeight="1">
       <c r="B231" s="6">
-        <f t="shared" si="20"/>
+        <f>B230</f>
         <v>46139</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -10717,7 +10723,7 @@
     </row>
     <row r="232" spans="2:7" ht="15.75" customHeight="1">
       <c r="B232" s="6">
-        <f t="shared" si="20"/>
+        <f>B231</f>
         <v>46139</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -10738,7 +10744,7 @@
     </row>
     <row r="233" spans="2:7" ht="15.75" customHeight="1">
       <c r="B233" s="6">
-        <f t="shared" si="20"/>
+        <f>B232</f>
         <v>46139</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -10779,7 +10785,7 @@
     </row>
     <row r="235" spans="2:7" ht="15.75" customHeight="1">
       <c r="B235" s="6">
-        <f t="shared" ref="B235:B238" si="21">B234</f>
+        <f>B234</f>
         <v>46140</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -10800,7 +10806,7 @@
     </row>
     <row r="236" spans="2:7" ht="15.75" customHeight="1">
       <c r="B236" s="6">
-        <f t="shared" si="21"/>
+        <f>B235</f>
         <v>46140</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -10821,7 +10827,7 @@
     </row>
     <row r="237" spans="2:7" ht="15.75" customHeight="1">
       <c r="B237" s="6">
-        <f t="shared" si="21"/>
+        <f>B236</f>
         <v>46140</v>
       </c>
       <c r="C237" s="4" t="s">
@@ -10842,7 +10848,7 @@
     </row>
     <row r="238" spans="2:7" ht="15.75" customHeight="1">
       <c r="B238" s="6">
-        <f t="shared" si="21"/>
+        <f>B237</f>
         <v>46140</v>
       </c>
       <c r="C238" s="8"/>
@@ -10875,7 +10881,7 @@
     </row>
     <row r="240" spans="2:7" ht="15.75" customHeight="1">
       <c r="B240" s="6">
-        <f t="shared" ref="B240:B263" si="22">B239</f>
+        <f t="shared" ref="B240:B263" si="16">B239</f>
         <v>46141</v>
       </c>
       <c r="C240" s="4" t="s">
@@ -10896,7 +10902,7 @@
     </row>
     <row r="241" spans="2:7" ht="15.75" customHeight="1">
       <c r="B241" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C241" s="4" t="s">
@@ -10917,7 +10923,7 @@
     </row>
     <row r="242" spans="2:7" ht="15.75" customHeight="1">
       <c r="B242" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C242" s="4" t="s">
@@ -10938,7 +10944,7 @@
     </row>
     <row r="243" spans="2:7" ht="15.75" customHeight="1">
       <c r="B243" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C243" s="4" t="s">
@@ -10959,7 +10965,7 @@
     </row>
     <row r="244" spans="2:7" ht="15.75" customHeight="1">
       <c r="B244" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C244" s="4" t="s">
@@ -10980,7 +10986,7 @@
     </row>
     <row r="245" spans="2:7" ht="15.75" customHeight="1">
       <c r="B245" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -11001,7 +11007,7 @@
     </row>
     <row r="246" spans="2:7" ht="15.75" customHeight="1">
       <c r="B246" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C246" s="4" t="s">
@@ -11022,7 +11028,7 @@
     </row>
     <row r="247" spans="2:7" ht="15.75" customHeight="1">
       <c r="B247" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C247" s="7" t="s">
@@ -11043,7 +11049,7 @@
     </row>
     <row r="248" spans="2:7" ht="15.75" customHeight="1">
       <c r="B248" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C248" s="7" t="s">
@@ -11064,7 +11070,7 @@
     </row>
     <row r="249" spans="2:7" ht="15.75" customHeight="1">
       <c r="B249" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C249" s="4" t="s">
@@ -11085,7 +11091,7 @@
     </row>
     <row r="250" spans="2:7" ht="15.75" customHeight="1">
       <c r="B250" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C250" s="4" t="s">
@@ -11106,7 +11112,7 @@
     </row>
     <row r="251" spans="2:7" ht="15.75" customHeight="1">
       <c r="B251" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C251" s="4" t="s">
@@ -11127,7 +11133,7 @@
     </row>
     <row r="252" spans="2:7" ht="15.75" customHeight="1">
       <c r="B252" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C252" s="4" t="s">
@@ -11148,7 +11154,7 @@
     </row>
     <row r="253" spans="2:7" ht="15.75" customHeight="1">
       <c r="B253" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C253" s="4" t="s">
@@ -11169,7 +11175,7 @@
     </row>
     <row r="254" spans="2:7" ht="15.75" customHeight="1">
       <c r="B254" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C254" s="4" t="s">
@@ -11190,7 +11196,7 @@
     </row>
     <row r="255" spans="2:7" ht="15.75" customHeight="1">
       <c r="B255" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C255" s="4" t="s">
@@ -11211,7 +11217,7 @@
     </row>
     <row r="256" spans="2:7" ht="15.75" customHeight="1">
       <c r="B256" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C256" s="4" t="s">
@@ -11232,7 +11238,7 @@
     </row>
     <row r="257" spans="2:7" ht="15.75" customHeight="1">
       <c r="B257" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C257" s="4" t="s">
@@ -11253,7 +11259,7 @@
     </row>
     <row r="258" spans="2:7" ht="15.75" customHeight="1">
       <c r="B258" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C258" s="4" t="s">
@@ -11274,7 +11280,7 @@
     </row>
     <row r="259" spans="2:7" ht="15.75" customHeight="1">
       <c r="B259" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C259" s="4" t="s">
@@ -11295,7 +11301,7 @@
     </row>
     <row r="260" spans="2:7" ht="15.75" customHeight="1">
       <c r="B260" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C260" s="4" t="s">
@@ -11316,7 +11322,7 @@
     </row>
     <row r="261" spans="2:7" ht="15.75" customHeight="1">
       <c r="B261" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C261" s="4" t="s">
@@ -11337,7 +11343,7 @@
     </row>
     <row r="262" spans="2:7" ht="15.75" customHeight="1">
       <c r="B262" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C262" s="4" t="s">
@@ -11358,7 +11364,7 @@
     </row>
     <row r="263" spans="2:7" ht="15.75" customHeight="1">
       <c r="B263" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>46141</v>
       </c>
       <c r="C263" s="4" t="s">
@@ -11399,7 +11405,7 @@
     </row>
     <row r="265" spans="2:7" ht="15.75" customHeight="1">
       <c r="B265" s="6">
-        <f t="shared" ref="B265:B278" si="23">B264</f>
+        <f t="shared" ref="B265:B278" si="17">B264</f>
         <v>46142</v>
       </c>
       <c r="C265" s="4" t="s">
@@ -11420,7 +11426,7 @@
     </row>
     <row r="266" spans="2:7" ht="15.75" customHeight="1">
       <c r="B266" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C266" s="4" t="s">
@@ -11441,7 +11447,7 @@
     </row>
     <row r="267" spans="2:7" ht="15.75" customHeight="1">
       <c r="B267" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C267" s="4" t="s">
@@ -11462,7 +11468,7 @@
     </row>
     <row r="268" spans="2:7" ht="15.75" customHeight="1">
       <c r="B268" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C268" s="4" t="s">
@@ -11483,7 +11489,7 @@
     </row>
     <row r="269" spans="2:7" ht="15.75" customHeight="1">
       <c r="B269" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C269" s="4" t="s">
@@ -11504,7 +11510,7 @@
     </row>
     <row r="270" spans="2:7" ht="15.75" customHeight="1">
       <c r="B270" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C270" s="4" t="s">
@@ -11525,7 +11531,7 @@
     </row>
     <row r="271" spans="2:7" ht="15.75" customHeight="1">
       <c r="B271" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C271" s="4" t="s">
@@ -11546,7 +11552,7 @@
     </row>
     <row r="272" spans="2:7" ht="15.75" customHeight="1">
       <c r="B272" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -11567,7 +11573,7 @@
     </row>
     <row r="273" spans="2:7" ht="15.75" customHeight="1">
       <c r="B273" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -11588,7 +11594,7 @@
     </row>
     <row r="274" spans="2:7" ht="15.75" customHeight="1">
       <c r="B274" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -11609,7 +11615,7 @@
     </row>
     <row r="275" spans="2:7" ht="15.75" customHeight="1">
       <c r="B275" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -11630,7 +11636,7 @@
     </row>
     <row r="276" spans="2:7" ht="15.75" customHeight="1">
       <c r="B276" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -11651,7 +11657,7 @@
     </row>
     <row r="277" spans="2:7" ht="15.75" customHeight="1">
       <c r="B277" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -11672,7 +11678,7 @@
     </row>
     <row r="278" spans="2:7" ht="15.75" customHeight="1">
       <c r="B278" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>46142</v>
       </c>
       <c r="C278" s="4" t="s">
@@ -11713,7 +11719,7 @@
     </row>
     <row r="280" spans="2:7" ht="15.75" customHeight="1">
       <c r="B280" s="6">
-        <f t="shared" ref="B280" si="24">B279</f>
+        <f>B279</f>
         <v>46143</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -11752,7 +11758,7 @@
     </row>
     <row r="282" spans="2:7" ht="15.75" customHeight="1">
       <c r="B282" s="6">
-        <f t="shared" ref="B282:B288" si="25">B281</f>
+        <f t="shared" ref="B282:B288" si="18">B281</f>
         <v>46144</v>
       </c>
       <c r="C282" s="4" t="s">
@@ -11773,7 +11779,7 @@
     </row>
     <row r="283" spans="2:7" ht="15.75" customHeight="1">
       <c r="B283" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -11794,7 +11800,7 @@
     </row>
     <row r="284" spans="2:7" ht="15.75" customHeight="1">
       <c r="B284" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -11815,7 +11821,7 @@
     </row>
     <row r="285" spans="2:7" ht="15.75" customHeight="1">
       <c r="B285" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -11836,7 +11842,7 @@
     </row>
     <row r="286" spans="2:7" ht="15.75" customHeight="1">
       <c r="B286" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C286" s="4" t="s">
@@ -11857,7 +11863,7 @@
     </row>
     <row r="287" spans="2:7" ht="15.75" customHeight="1">
       <c r="B287" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C287" s="4" t="s">
@@ -11878,7 +11884,7 @@
     </row>
     <row r="288" spans="2:7" ht="15.75" customHeight="1">
       <c r="B288" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>46144</v>
       </c>
       <c r="C288" s="4" t="s">
@@ -11919,7 +11925,7 @@
     </row>
     <row r="290" spans="2:7" ht="15.75" customHeight="1">
       <c r="B290" s="6">
-        <f t="shared" ref="B290:B299" si="26">B289</f>
+        <f t="shared" ref="B290:B299" si="19">B289</f>
         <v>46145</v>
       </c>
       <c r="C290" s="4" t="s">
@@ -11940,7 +11946,7 @@
     </row>
     <row r="291" spans="2:7" ht="15.75" customHeight="1">
       <c r="B291" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C291" s="4" t="s">
@@ -11961,7 +11967,7 @@
     </row>
     <row r="292" spans="2:7" ht="15.75" customHeight="1">
       <c r="B292" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C292" s="4" t="s">
@@ -11982,7 +11988,7 @@
     </row>
     <row r="293" spans="2:7" ht="15.75" customHeight="1">
       <c r="B293" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C293" s="4" t="s">
@@ -12003,7 +12009,7 @@
     </row>
     <row r="294" spans="2:7" ht="15.75" customHeight="1">
       <c r="B294" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C294" s="4" t="s">
@@ -12024,7 +12030,7 @@
     </row>
     <row r="295" spans="2:7" ht="15.75" customHeight="1">
       <c r="B295" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C295" s="4" t="s">
@@ -12045,7 +12051,7 @@
     </row>
     <row r="296" spans="2:7" ht="15.75" customHeight="1">
       <c r="B296" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -12066,7 +12072,7 @@
     </row>
     <row r="297" spans="2:7" ht="15.75" customHeight="1">
       <c r="B297" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C297" s="4" t="s">
@@ -12087,7 +12093,7 @@
     </row>
     <row r="298" spans="2:7" ht="15.75" customHeight="1">
       <c r="B298" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C298" s="4" t="s">
@@ -12108,7 +12114,7 @@
     </row>
     <row r="299" spans="2:7" ht="15.75" customHeight="1">
       <c r="B299" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="19"/>
         <v>46145</v>
       </c>
       <c r="C299" s="4" t="s">
@@ -12149,7 +12155,7 @@
     </row>
     <row r="301" spans="2:7" ht="15.75" customHeight="1">
       <c r="B301" s="6">
-        <f t="shared" ref="B301:B331" si="27">B300</f>
+        <f t="shared" ref="B301:B331" si="20">B300</f>
         <v>46146</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -12170,7 +12176,7 @@
     </row>
     <row r="302" spans="2:7" ht="15.75" customHeight="1">
       <c r="B302" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C302" s="4" t="s">
@@ -12191,7 +12197,7 @@
     </row>
     <row r="303" spans="2:7" ht="15.75" customHeight="1">
       <c r="B303" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C303" s="4" t="s">
@@ -12212,7 +12218,7 @@
     </row>
     <row r="304" spans="2:7" ht="15.75" customHeight="1">
       <c r="B304" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C304" s="4" t="s">
@@ -12233,7 +12239,7 @@
     </row>
     <row r="305" spans="2:7" ht="15.75" customHeight="1">
       <c r="B305" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C305" s="4" t="s">
@@ -12254,7 +12260,7 @@
     </row>
     <row r="306" spans="2:7" ht="15.75" customHeight="1">
       <c r="B306" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C306" s="4" t="s">
@@ -12275,7 +12281,7 @@
     </row>
     <row r="307" spans="2:7" ht="15.75" customHeight="1">
       <c r="B307" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C307" s="4" t="s">
@@ -12296,7 +12302,7 @@
     </row>
     <row r="308" spans="2:7" ht="15.75" customHeight="1">
       <c r="B308" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C308" s="4" t="s">
@@ -12317,7 +12323,7 @@
     </row>
     <row r="309" spans="2:7" ht="15.75" customHeight="1">
       <c r="B309" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C309" s="4" t="s">
@@ -12338,7 +12344,7 @@
     </row>
     <row r="310" spans="2:7" ht="15.75" customHeight="1">
       <c r="B310" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C310" s="4" t="s">
@@ -12359,7 +12365,7 @@
     </row>
     <row r="311" spans="2:7" ht="15.75" customHeight="1">
       <c r="B311" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C311" s="4" t="s">
@@ -12380,7 +12386,7 @@
     </row>
     <row r="312" spans="2:7" ht="15.75" customHeight="1">
       <c r="B312" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C312" s="4" t="s">
@@ -12401,7 +12407,7 @@
     </row>
     <row r="313" spans="2:7" ht="15.75" customHeight="1">
       <c r="B313" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C313" s="4" t="s">
@@ -12422,7 +12428,7 @@
     </row>
     <row r="314" spans="2:7" ht="15.75" customHeight="1">
       <c r="B314" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C314" s="4" t="s">
@@ -12443,7 +12449,7 @@
     </row>
     <row r="315" spans="2:7" ht="15.75" customHeight="1">
       <c r="B315" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C315" s="4" t="s">
@@ -12464,7 +12470,7 @@
     </row>
     <row r="316" spans="2:7" ht="15.75" customHeight="1">
       <c r="B316" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C316" s="4" t="s">
@@ -12485,7 +12491,7 @@
     </row>
     <row r="317" spans="2:7" ht="15.75" customHeight="1">
       <c r="B317" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C317" s="4" t="s">
@@ -12506,7 +12512,7 @@
     </row>
     <row r="318" spans="2:7" ht="15.75" customHeight="1">
       <c r="B318" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C318" s="4" t="s">
@@ -12527,7 +12533,7 @@
     </row>
     <row r="319" spans="2:7" ht="15.75" customHeight="1">
       <c r="B319" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C319" s="4" t="s">
@@ -12548,7 +12554,7 @@
     </row>
     <row r="320" spans="2:7" ht="15.75" customHeight="1">
       <c r="B320" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C320" s="4" t="s">
@@ -12569,7 +12575,7 @@
     </row>
     <row r="321" spans="2:7" ht="15.75" customHeight="1">
       <c r="B321" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C321" s="4" t="s">
@@ -12590,7 +12596,7 @@
     </row>
     <row r="322" spans="2:7" ht="15.75" customHeight="1">
       <c r="B322" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C322" s="4" t="s">
@@ -12611,7 +12617,7 @@
     </row>
     <row r="323" spans="2:7" ht="15.75" customHeight="1">
       <c r="B323" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C323" s="4" t="s">
@@ -12632,7 +12638,7 @@
     </row>
     <row r="324" spans="2:7" ht="15.75" customHeight="1">
       <c r="B324" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C324" s="4" t="s">
@@ -12653,7 +12659,7 @@
     </row>
     <row r="325" spans="2:7" ht="15.75" customHeight="1">
       <c r="B325" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C325" s="4" t="s">
@@ -12674,7 +12680,7 @@
     </row>
     <row r="326" spans="2:7" ht="15.75" customHeight="1">
       <c r="B326" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C326" s="4" t="s">
@@ -12695,7 +12701,7 @@
     </row>
     <row r="327" spans="2:7" ht="15.75" customHeight="1">
       <c r="B327" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C327" s="4" t="s">
@@ -12716,7 +12722,7 @@
     </row>
     <row r="328" spans="2:7" ht="15.75" customHeight="1">
       <c r="B328" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C328" s="4" t="s">
@@ -12737,7 +12743,7 @@
     </row>
     <row r="329" spans="2:7" ht="15.75" customHeight="1">
       <c r="B329" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C329" s="4" t="s">
@@ -12758,7 +12764,7 @@
     </row>
     <row r="330" spans="2:7" ht="15.75" customHeight="1">
       <c r="B330" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C330" s="4" t="s">
@@ -12779,7 +12785,7 @@
     </row>
     <row r="331" spans="2:7" ht="15.75" customHeight="1">
       <c r="B331" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="20"/>
         <v>46146</v>
       </c>
       <c r="C331" s="4" t="s">
@@ -12820,7 +12826,7 @@
     </row>
     <row r="333" spans="2:7" ht="15.75" customHeight="1">
       <c r="B333" s="6">
-        <f t="shared" ref="B333:B335" si="28">B332</f>
+        <f>B332</f>
         <v>46147</v>
       </c>
       <c r="C333" s="4" t="s">
@@ -12841,7 +12847,7 @@
     </row>
     <row r="334" spans="2:7" ht="15.75" customHeight="1">
       <c r="B334" s="6">
-        <f t="shared" si="28"/>
+        <f>B333</f>
         <v>46147</v>
       </c>
       <c r="C334" s="4" t="s">
@@ -12862,7 +12868,7 @@
     </row>
     <row r="335" spans="2:7" ht="15.75" customHeight="1">
       <c r="B335" s="6">
-        <f t="shared" si="28"/>
+        <f>B334</f>
         <v>46147</v>
       </c>
       <c r="C335" s="4" t="s">
@@ -12903,7 +12909,7 @@
     </row>
     <row r="337" spans="2:7" ht="15.75" customHeight="1">
       <c r="B337" s="6">
-        <f t="shared" ref="B337:B347" si="29">B336</f>
+        <f t="shared" ref="B337:B347" si="21">B336</f>
         <v>46148</v>
       </c>
       <c r="C337" s="4" t="s">
@@ -12924,7 +12930,7 @@
     </row>
     <row r="338" spans="2:7" ht="15.75" customHeight="1">
       <c r="B338" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C338" s="4" t="s">
@@ -12945,7 +12951,7 @@
     </row>
     <row r="339" spans="2:7" ht="15.75" customHeight="1">
       <c r="B339" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C339" s="4" t="s">
@@ -12966,7 +12972,7 @@
     </row>
     <row r="340" spans="2:7" ht="15.75" customHeight="1">
       <c r="B340" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C340" s="4" t="s">
@@ -12987,7 +12993,7 @@
     </row>
     <row r="341" spans="2:7" ht="15.75" customHeight="1">
       <c r="B341" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C341" s="4" t="s">
@@ -13008,7 +13014,7 @@
     </row>
     <row r="342" spans="2:7" ht="15.75" customHeight="1">
       <c r="B342" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C342" s="4" t="s">
@@ -13029,7 +13035,7 @@
     </row>
     <row r="343" spans="2:7" ht="15.75" customHeight="1">
       <c r="B343" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C343" s="4" t="s">
@@ -13050,7 +13056,7 @@
     </row>
     <row r="344" spans="2:7" ht="15.75" customHeight="1">
       <c r="B344" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C344" s="4" t="s">
@@ -13071,7 +13077,7 @@
     </row>
     <row r="345" spans="2:7" ht="15.75" customHeight="1">
       <c r="B345" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C345" s="4" t="s">
@@ -13092,7 +13098,7 @@
     </row>
     <row r="346" spans="2:7" ht="15.75" customHeight="1">
       <c r="B346" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C346" s="4" t="s">
@@ -13113,7 +13119,7 @@
     </row>
     <row r="347" spans="2:7" ht="15.75" customHeight="1">
       <c r="B347" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>46148</v>
       </c>
       <c r="C347" s="8"/>
@@ -13152,7 +13158,7 @@
     </row>
     <row r="349" spans="2:7" ht="15.75" customHeight="1">
       <c r="B349" s="6">
-        <f t="shared" ref="B349:B367" si="30">B348</f>
+        <f t="shared" ref="B349:B367" si="22">B348</f>
         <v>46149</v>
       </c>
       <c r="C349" s="7" t="s">
@@ -13173,7 +13179,7 @@
     </row>
     <row r="350" spans="2:7" ht="15.75" customHeight="1">
       <c r="B350" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C350" s="4" t="s">
@@ -13194,7 +13200,7 @@
     </row>
     <row r="351" spans="2:7" ht="15.75" customHeight="1">
       <c r="B351" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C351" s="4" t="s">
@@ -13215,7 +13221,7 @@
     </row>
     <row r="352" spans="2:7" ht="15.75" customHeight="1">
       <c r="B352" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C352" s="4" t="s">
@@ -13236,7 +13242,7 @@
     </row>
     <row r="353" spans="2:7" ht="15.75" customHeight="1">
       <c r="B353" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C353" s="4" t="s">
@@ -13257,7 +13263,7 @@
     </row>
     <row r="354" spans="2:7" ht="15.75" customHeight="1">
       <c r="B354" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C354" s="4" t="s">
@@ -13278,7 +13284,7 @@
     </row>
     <row r="355" spans="2:7" ht="15.75" customHeight="1">
       <c r="B355" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C355" s="4" t="s">
@@ -13299,7 +13305,7 @@
     </row>
     <row r="356" spans="2:7" ht="15.75" customHeight="1">
       <c r="B356" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C356" s="4" t="s">
@@ -13320,7 +13326,7 @@
     </row>
     <row r="357" spans="2:7" ht="15.75" customHeight="1">
       <c r="B357" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C357" s="4" t="s">
@@ -13341,7 +13347,7 @@
     </row>
     <row r="358" spans="2:7" ht="15.75" customHeight="1">
       <c r="B358" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C358" s="4" t="s">
@@ -13362,7 +13368,7 @@
     </row>
     <row r="359" spans="2:7" ht="15.75" customHeight="1">
       <c r="B359" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C359" s="4" t="s">
@@ -13383,7 +13389,7 @@
     </row>
     <row r="360" spans="2:7" ht="15.75" customHeight="1">
       <c r="B360" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C360" s="4" t="s">
@@ -13404,7 +13410,7 @@
     </row>
     <row r="361" spans="2:7" ht="15.75" customHeight="1">
       <c r="B361" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C361" s="4" t="s">
@@ -13425,7 +13431,7 @@
     </row>
     <row r="362" spans="2:7" ht="15.75" customHeight="1">
       <c r="B362" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C362" s="4" t="s">
@@ -13446,7 +13452,7 @@
     </row>
     <row r="363" spans="2:7" ht="15.75" customHeight="1">
       <c r="B363" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C363" s="4" t="s">
@@ -13467,7 +13473,7 @@
     </row>
     <row r="364" spans="2:7" ht="15.75" customHeight="1">
       <c r="B364" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C364" s="4" t="s">
@@ -13488,7 +13494,7 @@
     </row>
     <row r="365" spans="2:7" ht="15.75" customHeight="1">
       <c r="B365" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C365" s="4" t="s">
@@ -13509,7 +13515,7 @@
     </row>
     <row r="366" spans="2:7" ht="15.75" customHeight="1">
       <c r="B366" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C366" s="4" t="s">
@@ -13530,7 +13536,7 @@
     </row>
     <row r="367" spans="2:7" ht="15.75" customHeight="1">
       <c r="B367" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>46149</v>
       </c>
       <c r="C367" s="4" t="s">
@@ -13571,7 +13577,7 @@
     </row>
     <row r="369" spans="2:7" ht="15.75" customHeight="1">
       <c r="B369" s="6">
-        <f t="shared" ref="B369:B382" si="31">B368</f>
+        <f t="shared" ref="B369:B382" si="23">B368</f>
         <v>46150</v>
       </c>
       <c r="C369" s="7" t="s">
@@ -13592,7 +13598,7 @@
     </row>
     <row r="370" spans="2:7" ht="15.75" customHeight="1">
       <c r="B370" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C370" s="7" t="s">
@@ -13613,7 +13619,7 @@
     </row>
     <row r="371" spans="2:7" ht="15.75" customHeight="1">
       <c r="B371" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C371" s="7" t="s">
@@ -13634,7 +13640,7 @@
     </row>
     <row r="372" spans="2:7" ht="15.75" customHeight="1">
       <c r="B372" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C372" s="7" t="s">
@@ -13655,7 +13661,7 @@
     </row>
     <row r="373" spans="2:7" ht="15.75" customHeight="1">
       <c r="B373" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C373" s="7" t="s">
@@ -13676,7 +13682,7 @@
     </row>
     <row r="374" spans="2:7" ht="15.75" customHeight="1">
       <c r="B374" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C374" s="7" t="s">
@@ -13697,7 +13703,7 @@
     </row>
     <row r="375" spans="2:7" ht="15.75" customHeight="1">
       <c r="B375" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C375" s="4" t="s">
@@ -13718,7 +13724,7 @@
     </row>
     <row r="376" spans="2:7" ht="15.75" customHeight="1">
       <c r="B376" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C376" s="4" t="s">
@@ -13739,7 +13745,7 @@
     </row>
     <row r="377" spans="2:7" ht="15.75" customHeight="1">
       <c r="B377" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C377" s="4" t="s">
@@ -13760,7 +13766,7 @@
     </row>
     <row r="378" spans="2:7" ht="15.75" customHeight="1">
       <c r="B378" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C378" s="4" t="s">
@@ -13779,7 +13785,7 @@
     </row>
     <row r="379" spans="2:7" ht="15.75" customHeight="1">
       <c r="B379" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C379" s="4" t="s">
@@ -13800,7 +13806,7 @@
     </row>
     <row r="380" spans="2:7" ht="15.75" customHeight="1">
       <c r="B380" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C380" s="4" t="s">
@@ -13821,7 +13827,7 @@
     </row>
     <row r="381" spans="2:7" ht="15.75" customHeight="1">
       <c r="B381" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C381" s="4" t="s">
@@ -13842,7 +13848,7 @@
     </row>
     <row r="382" spans="2:7" ht="15.75" customHeight="1">
       <c r="B382" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="23"/>
         <v>46150</v>
       </c>
       <c r="C382" s="4" t="s">
@@ -13883,7 +13889,7 @@
     </row>
     <row r="384" spans="2:7" ht="15.75" customHeight="1">
       <c r="B384" s="6">
-        <f t="shared" ref="B384:B391" si="32">B383</f>
+        <f t="shared" ref="B384:B391" si="24">B383</f>
         <v>46151</v>
       </c>
       <c r="C384" s="4" t="s">
@@ -13904,7 +13910,7 @@
     </row>
     <row r="385" spans="2:7" ht="15.75" customHeight="1">
       <c r="B385" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C385" s="4" t="s">
@@ -13925,7 +13931,7 @@
     </row>
     <row r="386" spans="2:7" ht="15.75" customHeight="1">
       <c r="B386" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C386" s="4" t="s">
@@ -13946,7 +13952,7 @@
     </row>
     <row r="387" spans="2:7" ht="15.75" customHeight="1">
       <c r="B387" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C387" s="4" t="s">
@@ -13967,7 +13973,7 @@
     </row>
     <row r="388" spans="2:7" ht="15.75" customHeight="1">
       <c r="B388" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C388" s="4" t="s">
@@ -13988,7 +13994,7 @@
     </row>
     <row r="389" spans="2:7" ht="15.75" customHeight="1">
       <c r="B389" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C389" s="4" t="s">
@@ -14009,7 +14015,7 @@
     </row>
     <row r="390" spans="2:7" ht="15.75" customHeight="1">
       <c r="B390" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C390" s="4" t="s">
@@ -14030,7 +14036,7 @@
     </row>
     <row r="391" spans="2:7" ht="15.75" customHeight="1">
       <c r="B391" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>46151</v>
       </c>
       <c r="C391" s="4" t="s">
@@ -14071,7 +14077,7 @@
     </row>
     <row r="393" spans="2:7" ht="15.75" customHeight="1">
       <c r="B393" s="6">
-        <f t="shared" ref="B393:B412" si="33">B392</f>
+        <f t="shared" ref="B393:B412" si="25">B392</f>
         <v>46152</v>
       </c>
       <c r="C393" s="7" t="s">
@@ -14092,7 +14098,7 @@
     </row>
     <row r="394" spans="2:7" ht="15.75" customHeight="1">
       <c r="B394" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C394" s="4" t="s">
@@ -14113,7 +14119,7 @@
     </row>
     <row r="395" spans="2:7" ht="15.75" customHeight="1">
       <c r="B395" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C395" s="4" t="s">
@@ -14134,7 +14140,7 @@
     </row>
     <row r="396" spans="2:7" ht="15.75" customHeight="1">
       <c r="B396" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C396" s="4" t="s">
@@ -14155,7 +14161,7 @@
     </row>
     <row r="397" spans="2:7" ht="15.75" customHeight="1">
       <c r="B397" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C397" s="4" t="s">
@@ -14176,7 +14182,7 @@
     </row>
     <row r="398" spans="2:7" ht="15.75" customHeight="1">
       <c r="B398" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C398" s="4" t="s">
@@ -14197,7 +14203,7 @@
     </row>
     <row r="399" spans="2:7" ht="15.75" customHeight="1">
       <c r="B399" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C399" s="4" t="s">
@@ -14218,7 +14224,7 @@
     </row>
     <row r="400" spans="2:7" ht="15.75" customHeight="1">
       <c r="B400" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C400" s="4" t="s">
@@ -14239,7 +14245,7 @@
     </row>
     <row r="401" spans="2:7" ht="15.75" customHeight="1">
       <c r="B401" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C401" s="4" t="s">
@@ -14260,7 +14266,7 @@
     </row>
     <row r="402" spans="2:7" ht="15.75" customHeight="1">
       <c r="B402" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C402" s="4" t="s">
@@ -14281,7 +14287,7 @@
     </row>
     <row r="403" spans="2:7" ht="15.75" customHeight="1">
       <c r="B403" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C403" s="4" t="s">
@@ -14302,7 +14308,7 @@
     </row>
     <row r="404" spans="2:7" ht="15.75" customHeight="1">
       <c r="B404" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C404" s="4" t="s">
@@ -14323,7 +14329,7 @@
     </row>
     <row r="405" spans="2:7" ht="15.75" customHeight="1">
       <c r="B405" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C405" s="4" t="s">
@@ -14344,7 +14350,7 @@
     </row>
     <row r="406" spans="2:7" ht="15.75" customHeight="1">
       <c r="B406" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C406" s="4" t="s">
@@ -14365,7 +14371,7 @@
     </row>
     <row r="407" spans="2:7" ht="15.75" customHeight="1">
       <c r="B407" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C407" s="4" t="s">
@@ -14386,7 +14392,7 @@
     </row>
     <row r="408" spans="2:7" ht="15.75" customHeight="1">
       <c r="B408" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C408" s="4" t="s">
@@ -14407,7 +14413,7 @@
     </row>
     <row r="409" spans="2:7" ht="15.75" customHeight="1">
       <c r="B409" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C409" s="4" t="s">
@@ -14428,7 +14434,7 @@
     </row>
     <row r="410" spans="2:7" ht="15.75" customHeight="1">
       <c r="B410" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C410" s="4" t="s">
@@ -14449,7 +14455,7 @@
     </row>
     <row r="411" spans="2:7" ht="15.75" customHeight="1">
       <c r="B411" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C411" s="4" t="s">
@@ -14470,7 +14476,7 @@
     </row>
     <row r="412" spans="2:7" ht="15.75" customHeight="1">
       <c r="B412" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="25"/>
         <v>46152</v>
       </c>
       <c r="C412" s="4" t="s">
@@ -14511,7 +14517,7 @@
     </row>
     <row r="414" spans="2:7" ht="15.75" customHeight="1">
       <c r="B414" s="6">
-        <f t="shared" ref="B414:B430" si="34">B413</f>
+        <f t="shared" ref="B414:B430" si="26">B413</f>
         <v>46153</v>
       </c>
       <c r="C414" s="4" t="s">
@@ -14532,7 +14538,7 @@
     </row>
     <row r="415" spans="2:7" ht="15.75" customHeight="1">
       <c r="B415" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C415" s="4" t="s">
@@ -14553,7 +14559,7 @@
     </row>
     <row r="416" spans="2:7" ht="15.75" customHeight="1">
       <c r="B416" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C416" s="4" t="s">
@@ -14574,7 +14580,7 @@
     </row>
     <row r="417" spans="2:7" ht="15.75" customHeight="1">
       <c r="B417" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C417" s="4" t="s">
@@ -14595,7 +14601,7 @@
     </row>
     <row r="418" spans="2:7" ht="15.75" customHeight="1">
       <c r="B418" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C418" s="4" t="s">
@@ -14616,7 +14622,7 @@
     </row>
     <row r="419" spans="2:7" ht="15.75" customHeight="1">
       <c r="B419" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C419" s="4" t="s">
@@ -14637,7 +14643,7 @@
     </row>
     <row r="420" spans="2:7" ht="15.75" customHeight="1">
       <c r="B420" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C420" s="4" t="s">
@@ -14658,7 +14664,7 @@
     </row>
     <row r="421" spans="2:7" ht="15.75" customHeight="1">
       <c r="B421" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C421" s="16" t="s">
@@ -14679,7 +14685,7 @@
     </row>
     <row r="422" spans="2:7" ht="15.75" customHeight="1">
       <c r="B422" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C422" s="4" t="s">
@@ -14700,7 +14706,7 @@
     </row>
     <row r="423" spans="2:7" ht="15.75" customHeight="1">
       <c r="B423" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C423" s="4" t="s">
@@ -14721,7 +14727,7 @@
     </row>
     <row r="424" spans="2:7" ht="15.75" customHeight="1">
       <c r="B424" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C424" s="4" t="s">
@@ -14742,7 +14748,7 @@
     </row>
     <row r="425" spans="2:7" ht="15.75" customHeight="1">
       <c r="B425" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C425" s="4" t="s">
@@ -14763,7 +14769,7 @@
     </row>
     <row r="426" spans="2:7" ht="15.75" customHeight="1">
       <c r="B426" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C426" s="4" t="s">
@@ -14784,7 +14790,7 @@
     </row>
     <row r="427" spans="2:7" ht="15.75" customHeight="1">
       <c r="B427" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C427" s="4" t="s">
@@ -14805,7 +14811,7 @@
     </row>
     <row r="428" spans="2:7" ht="15.75" customHeight="1">
       <c r="B428" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C428" s="4" t="s">
@@ -14826,7 +14832,7 @@
     </row>
     <row r="429" spans="2:7" ht="15.75" customHeight="1">
       <c r="B429" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C429" s="4" t="s">
@@ -14847,7 +14853,7 @@
     </row>
     <row r="430" spans="2:7" ht="15.75" customHeight="1">
       <c r="B430" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="26"/>
         <v>46153</v>
       </c>
       <c r="C430" s="4" t="s">
@@ -14888,7 +14894,7 @@
     </row>
     <row r="432" spans="2:7" ht="15.75" customHeight="1">
       <c r="B432" s="6">
-        <f t="shared" ref="B432:B441" si="35">B431</f>
+        <f t="shared" ref="B432:B441" si="27">B431</f>
         <v>46154</v>
       </c>
       <c r="C432" s="7" t="s">
@@ -14909,7 +14915,7 @@
     </row>
     <row r="433" spans="2:7" ht="15.75" customHeight="1">
       <c r="B433" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C433" s="7" t="s">
@@ -14930,7 +14936,7 @@
     </row>
     <row r="434" spans="2:7" ht="15.75" customHeight="1">
       <c r="B434" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C434" s="7" t="s">
@@ -14951,7 +14957,7 @@
     </row>
     <row r="435" spans="2:7" ht="15.75" customHeight="1">
       <c r="B435" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C435" s="7" t="s">
@@ -14972,7 +14978,7 @@
     </row>
     <row r="436" spans="2:7" ht="15.75" customHeight="1">
       <c r="B436" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C436" s="7" t="s">
@@ -14993,7 +14999,7 @@
     </row>
     <row r="437" spans="2:7" ht="15.75" customHeight="1">
       <c r="B437" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C437" s="7" t="s">
@@ -15014,7 +15020,7 @@
     </row>
     <row r="438" spans="2:7" ht="15.75" customHeight="1">
       <c r="B438" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C438" s="7" t="s">
@@ -15035,7 +15041,7 @@
     </row>
     <row r="439" spans="2:7" ht="15.75" customHeight="1">
       <c r="B439" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C439" s="7" t="s">
@@ -15056,7 +15062,7 @@
     </row>
     <row r="440" spans="2:7" ht="15.75" customHeight="1">
       <c r="B440" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C440" s="4" t="s">
@@ -15077,7 +15083,7 @@
     </row>
     <row r="441" spans="2:7" ht="15.75" customHeight="1">
       <c r="B441" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="27"/>
         <v>46154</v>
       </c>
       <c r="C441" s="4" t="s">
@@ -15118,7 +15124,7 @@
     </row>
     <row r="443" spans="2:7" ht="15.75" customHeight="1">
       <c r="B443" s="6">
-        <f t="shared" ref="B443:B445" si="36">B442</f>
+        <f>B442</f>
         <v>46155</v>
       </c>
       <c r="C443" s="7" t="s">
@@ -15139,7 +15145,7 @@
     </row>
     <row r="444" spans="2:7" ht="15.75" customHeight="1">
       <c r="B444" s="6">
-        <f t="shared" si="36"/>
+        <f>B443</f>
         <v>46155</v>
       </c>
       <c r="C444" s="7" t="s">
@@ -15160,7 +15166,7 @@
     </row>
     <row r="445" spans="2:7" ht="15.75" customHeight="1">
       <c r="B445" s="6">
-        <f t="shared" si="36"/>
+        <f>B444</f>
         <v>46155</v>
       </c>
       <c r="C445" s="16" t="s">
@@ -15201,7 +15207,7 @@
     </row>
     <row r="447" spans="2:7" ht="15.75" customHeight="1">
       <c r="B447" s="6">
-        <f t="shared" ref="B447:B460" si="37">B446</f>
+        <f t="shared" ref="B447:B460" si="28">B446</f>
         <v>46156</v>
       </c>
       <c r="C447" s="4" t="s">
@@ -15222,7 +15228,7 @@
     </row>
     <row r="448" spans="2:7" ht="15.75" customHeight="1">
       <c r="B448" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C448" s="4" t="s">
@@ -15243,7 +15249,7 @@
     </row>
     <row r="449" spans="2:7" ht="15.75" customHeight="1">
       <c r="B449" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C449" s="4" t="s">
@@ -15264,7 +15270,7 @@
     </row>
     <row r="450" spans="2:7" ht="15.75" customHeight="1">
       <c r="B450" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C450" s="4" t="s">
@@ -15285,7 +15291,7 @@
     </row>
     <row r="451" spans="2:7" ht="15.75" customHeight="1">
       <c r="B451" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C451" s="4" t="s">
@@ -15306,7 +15312,7 @@
     </row>
     <row r="452" spans="2:7" ht="15.75" customHeight="1">
       <c r="B452" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C452" s="4" t="s">
@@ -15327,7 +15333,7 @@
     </row>
     <row r="453" spans="2:7" ht="15.75" customHeight="1">
       <c r="B453" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C453" s="4" t="s">
@@ -15348,7 +15354,7 @@
     </row>
     <row r="454" spans="2:7" ht="15.75" customHeight="1">
       <c r="B454" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C454" s="4" t="s">
@@ -15369,7 +15375,7 @@
     </row>
     <row r="455" spans="2:7" ht="15.75" customHeight="1">
       <c r="B455" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C455" s="4" t="s">
@@ -15390,7 +15396,7 @@
     </row>
     <row r="456" spans="2:7" ht="15.75" customHeight="1">
       <c r="B456" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C456" s="4" t="s">
@@ -15411,7 +15417,7 @@
     </row>
     <row r="457" spans="2:7" ht="15.75" customHeight="1">
       <c r="B457" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C457" s="4" t="s">
@@ -15432,7 +15438,7 @@
     </row>
     <row r="458" spans="2:7" ht="15.75" customHeight="1">
       <c r="B458" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C458" s="4" t="s">
@@ -15453,7 +15459,7 @@
     </row>
     <row r="459" spans="2:7" ht="15.75" customHeight="1">
       <c r="B459" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C459" s="4" t="s">
@@ -15474,7 +15480,7 @@
     </row>
     <row r="460" spans="2:7" ht="15.75" customHeight="1">
       <c r="B460" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="C460" s="4" t="s">
@@ -15515,7 +15521,7 @@
     </row>
     <row r="462" spans="2:7" ht="15.75" customHeight="1">
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B489" si="38">B461</f>
+        <f t="shared" ref="B462:B489" si="29">B461</f>
         <v>46157</v>
       </c>
       <c r="C462" s="4" t="s">
@@ -15536,7 +15542,7 @@
     </row>
     <row r="463" spans="2:7" ht="15.75" customHeight="1">
       <c r="B463" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C463" s="4" t="s">
@@ -15557,7 +15563,7 @@
     </row>
     <row r="464" spans="2:7" ht="15.75" customHeight="1">
       <c r="B464" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C464" s="4" t="s">
@@ -15578,7 +15584,7 @@
     </row>
     <row r="465" spans="2:7" ht="15.75" customHeight="1">
       <c r="B465" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C465" s="4" t="s">
@@ -15599,7 +15605,7 @@
     </row>
     <row r="466" spans="2:7" ht="15.75" customHeight="1">
       <c r="B466" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C466" s="4" t="s">
@@ -15620,7 +15626,7 @@
     </row>
     <row r="467" spans="2:7" ht="15.75" customHeight="1">
       <c r="B467" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C467" s="4" t="s">
@@ -15641,7 +15647,7 @@
     </row>
     <row r="468" spans="2:7" ht="15.75" customHeight="1">
       <c r="B468" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C468" s="4" t="s">
@@ -15662,7 +15668,7 @@
     </row>
     <row r="469" spans="2:7" ht="15.75" customHeight="1">
       <c r="B469" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C469" s="4" t="s">
@@ -15683,7 +15689,7 @@
     </row>
     <row r="470" spans="2:7" ht="15.75" customHeight="1">
       <c r="B470" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C470" s="4" t="s">
@@ -15704,7 +15710,7 @@
     </row>
     <row r="471" spans="2:7" ht="15.75" customHeight="1">
       <c r="B471" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C471" s="4" t="s">
@@ -15725,7 +15731,7 @@
     </row>
     <row r="472" spans="2:7" ht="15.75" customHeight="1">
       <c r="B472" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C472" s="4" t="s">
@@ -15746,7 +15752,7 @@
     </row>
     <row r="473" spans="2:7" ht="15.75" customHeight="1">
       <c r="B473" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C473" s="4" t="s">
@@ -15767,7 +15773,7 @@
     </row>
     <row r="474" spans="2:7" ht="15.75" customHeight="1">
       <c r="B474" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C474" s="4" t="s">
@@ -15788,7 +15794,7 @@
     </row>
     <row r="475" spans="2:7" ht="15.75" customHeight="1">
       <c r="B475" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C475" s="4" t="s">
@@ -15809,7 +15815,7 @@
     </row>
     <row r="476" spans="2:7" ht="15.75" customHeight="1">
       <c r="B476" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C476" s="4" t="s">
@@ -15830,7 +15836,7 @@
     </row>
     <row r="477" spans="2:7" ht="15.75" customHeight="1">
       <c r="B477" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C477" s="4" t="s">
@@ -15851,7 +15857,7 @@
     </row>
     <row r="478" spans="2:7" ht="15.75" customHeight="1">
       <c r="B478" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C478" s="4" t="s">
@@ -15872,7 +15878,7 @@
     </row>
     <row r="479" spans="2:7" ht="15.75" customHeight="1">
       <c r="B479" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C479" s="4" t="s">
@@ -15893,7 +15899,7 @@
     </row>
     <row r="480" spans="2:7" ht="15.75" customHeight="1">
       <c r="B480" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C480" s="4" t="s">
@@ -15914,7 +15920,7 @@
     </row>
     <row r="481" spans="2:7" ht="15.75" customHeight="1">
       <c r="B481" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C481" s="4" t="s">
@@ -15935,7 +15941,7 @@
     </row>
     <row r="482" spans="2:7" ht="15.75" customHeight="1">
       <c r="B482" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C482" s="4" t="s">
@@ -15956,7 +15962,7 @@
     </row>
     <row r="483" spans="2:7" ht="15.75" customHeight="1">
       <c r="B483" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C483" s="4" t="s">
@@ -15977,7 +15983,7 @@
     </row>
     <row r="484" spans="2:7" ht="15.75" customHeight="1">
       <c r="B484" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C484" s="4" t="s">
@@ -15998,7 +16004,7 @@
     </row>
     <row r="485" spans="2:7" ht="15.75" customHeight="1">
       <c r="B485" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C485" s="4" t="s">
@@ -16019,7 +16025,7 @@
     </row>
     <row r="486" spans="2:7" ht="15.75" customHeight="1">
       <c r="B486" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C486" s="4" t="s">
@@ -16040,7 +16046,7 @@
     </row>
     <row r="487" spans="2:7" ht="15.75" customHeight="1">
       <c r="B487" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C487" s="4" t="s">
@@ -16061,7 +16067,7 @@
     </row>
     <row r="488" spans="2:7" ht="15.75" customHeight="1">
       <c r="B488" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C488" s="4" t="s">
@@ -16082,7 +16088,7 @@
     </row>
     <row r="489" spans="2:7" ht="15.75" customHeight="1">
       <c r="B489" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="C489" s="4" t="s">
@@ -16123,7 +16129,7 @@
     </row>
     <row r="491" spans="2:7" ht="15.75" customHeight="1">
       <c r="B491" s="6">
-        <f t="shared" ref="B491:B507" si="39">B490</f>
+        <f t="shared" ref="B491:B507" si="30">B490</f>
         <v>46158</v>
       </c>
       <c r="C491" s="7" t="s">
@@ -16144,7 +16150,7 @@
     </row>
     <row r="492" spans="2:7" ht="15.75" customHeight="1">
       <c r="B492" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C492" s="4" t="s">
@@ -16165,7 +16171,7 @@
     </row>
     <row r="493" spans="2:7" ht="15.75" customHeight="1">
       <c r="B493" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C493" s="4" t="s">
@@ -16186,7 +16192,7 @@
     </row>
     <row r="494" spans="2:7" ht="15.75" customHeight="1">
       <c r="B494" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C494" s="4" t="s">
@@ -16207,7 +16213,7 @@
     </row>
     <row r="495" spans="2:7" ht="15.75" customHeight="1">
       <c r="B495" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C495" s="4" t="s">
@@ -16228,7 +16234,7 @@
     </row>
     <row r="496" spans="2:7" ht="15.75" customHeight="1">
       <c r="B496" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C496" s="4" t="s">
@@ -16249,7 +16255,7 @@
     </row>
     <row r="497" spans="2:7" ht="15.75" customHeight="1">
       <c r="B497" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C497" s="4" t="s">
@@ -16270,7 +16276,7 @@
     </row>
     <row r="498" spans="2:7" ht="15.75" customHeight="1">
       <c r="B498" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C498" s="4" t="s">
@@ -16291,7 +16297,7 @@
     </row>
     <row r="499" spans="2:7" ht="15.75" customHeight="1">
       <c r="B499" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C499" s="4" t="s">
@@ -16312,7 +16318,7 @@
     </row>
     <row r="500" spans="2:7" ht="15.75" customHeight="1">
       <c r="B500" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C500" s="4" t="s">
@@ -16333,7 +16339,7 @@
     </row>
     <row r="501" spans="2:7" ht="15.75" customHeight="1">
       <c r="B501" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C501" s="4" t="s">
@@ -16354,7 +16360,7 @@
     </row>
     <row r="502" spans="2:7" ht="15.75" customHeight="1">
       <c r="B502" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C502" s="4" t="s">
@@ -16375,7 +16381,7 @@
     </row>
     <row r="503" spans="2:7" ht="15.75" customHeight="1">
       <c r="B503" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C503" s="4" t="s">
@@ -16396,7 +16402,7 @@
     </row>
     <row r="504" spans="2:7" ht="15.75" customHeight="1">
       <c r="B504" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C504" s="4" t="s">
@@ -16417,7 +16423,7 @@
     </row>
     <row r="505" spans="2:7" ht="15.75" customHeight="1">
       <c r="B505" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C505" s="4" t="s">
@@ -16438,7 +16444,7 @@
     </row>
     <row r="506" spans="2:7" ht="15.75" customHeight="1">
       <c r="B506" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C506" s="4" t="s">
@@ -16459,7 +16465,7 @@
     </row>
     <row r="507" spans="2:7" ht="15.75" customHeight="1">
       <c r="B507" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="30"/>
         <v>46158</v>
       </c>
       <c r="C507" s="4" t="s">
@@ -16500,7 +16506,7 @@
     </row>
     <row r="509" spans="2:7" ht="15.75" customHeight="1">
       <c r="B509" s="6">
-        <f t="shared" ref="B509:B527" si="40">B508</f>
+        <f t="shared" ref="B509:B527" si="31">B508</f>
         <v>46159</v>
       </c>
       <c r="C509" s="4" t="s">
@@ -16521,7 +16527,7 @@
     </row>
     <row r="510" spans="2:7" ht="15.75" customHeight="1">
       <c r="B510" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C510" s="4" t="s">
@@ -16542,7 +16548,7 @@
     </row>
     <row r="511" spans="2:7" ht="15.75" customHeight="1">
       <c r="B511" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C511" s="4" t="s">
@@ -16563,7 +16569,7 @@
     </row>
     <row r="512" spans="2:7" ht="15.75" customHeight="1">
       <c r="B512" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C512" s="4" t="s">
@@ -16584,7 +16590,7 @@
     </row>
     <row r="513" spans="2:7" ht="15.75" customHeight="1">
       <c r="B513" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C513" s="4" t="s">
@@ -16605,7 +16611,7 @@
     </row>
     <row r="514" spans="2:7" ht="15.75" customHeight="1">
       <c r="B514" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C514" s="4" t="s">
@@ -16626,7 +16632,7 @@
     </row>
     <row r="515" spans="2:7" ht="15.75" customHeight="1">
       <c r="B515" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C515" s="4" t="s">
@@ -16647,7 +16653,7 @@
     </row>
     <row r="516" spans="2:7" ht="15.75" customHeight="1">
       <c r="B516" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C516" s="4" t="s">
@@ -16668,7 +16674,7 @@
     </row>
     <row r="517" spans="2:7" ht="15.75" customHeight="1">
       <c r="B517" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C517" s="4" t="s">
@@ -16689,7 +16695,7 @@
     </row>
     <row r="518" spans="2:7" ht="15.75" customHeight="1">
       <c r="B518" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C518" s="4" t="s">
@@ -16710,7 +16716,7 @@
     </row>
     <row r="519" spans="2:7" ht="15.75" customHeight="1">
       <c r="B519" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C519" s="4" t="s">
@@ -16731,7 +16737,7 @@
     </row>
     <row r="520" spans="2:7" ht="15.75" customHeight="1">
       <c r="B520" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C520" s="4" t="s">
@@ -16752,7 +16758,7 @@
     </row>
     <row r="521" spans="2:7" ht="15.75" customHeight="1">
       <c r="B521" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C521" s="4" t="s">
@@ -16773,7 +16779,7 @@
     </row>
     <row r="522" spans="2:7" ht="15.75" customHeight="1">
       <c r="B522" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C522" s="4" t="s">
@@ -16794,7 +16800,7 @@
     </row>
     <row r="523" spans="2:7" ht="15.75" customHeight="1">
       <c r="B523" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C523" s="4" t="s">
@@ -16815,7 +16821,7 @@
     </row>
     <row r="524" spans="2:7" ht="15.75" customHeight="1">
       <c r="B524" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C524" s="4" t="s">
@@ -16836,7 +16842,7 @@
     </row>
     <row r="525" spans="2:7" ht="15.75" customHeight="1">
       <c r="B525" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C525" s="4" t="s">
@@ -16857,7 +16863,7 @@
     </row>
     <row r="526" spans="2:7" ht="15.75" customHeight="1">
       <c r="B526" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C526" s="4" t="s">
@@ -16878,7 +16884,7 @@
     </row>
     <row r="527" spans="2:7" ht="15.75" customHeight="1">
       <c r="B527" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
         <v>46159</v>
       </c>
       <c r="C527" s="4" t="s">
@@ -16919,7 +16925,7 @@
     </row>
     <row r="529" spans="2:7" ht="15.75" customHeight="1">
       <c r="B529" s="6">
-        <f t="shared" ref="B529:B567" si="41">B528</f>
+        <f t="shared" ref="B529:B567" si="32">B528</f>
         <v>46161</v>
       </c>
       <c r="C529" s="4" t="s">
@@ -16940,7 +16946,7 @@
     </row>
     <row r="530" spans="2:7" ht="15.75" customHeight="1">
       <c r="B530" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C530" s="4" t="s">
@@ -16961,7 +16967,7 @@
     </row>
     <row r="531" spans="2:7" ht="15.75" customHeight="1">
       <c r="B531" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C531" s="4" t="s">
@@ -16982,7 +16988,7 @@
     </row>
     <row r="532" spans="2:7" ht="15.75" customHeight="1">
       <c r="B532" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C532" s="4" t="s">
@@ -17003,7 +17009,7 @@
     </row>
     <row r="533" spans="2:7" ht="15.75" customHeight="1">
       <c r="B533" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C533" s="4" t="s">
@@ -17024,7 +17030,7 @@
     </row>
     <row r="534" spans="2:7" ht="15.75" customHeight="1">
       <c r="B534" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C534" s="4" t="s">
@@ -17045,7 +17051,7 @@
     </row>
     <row r="535" spans="2:7" ht="15.75" customHeight="1">
       <c r="B535" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C535" s="4" t="s">
@@ -17066,7 +17072,7 @@
     </row>
     <row r="536" spans="2:7" ht="15.75" customHeight="1">
       <c r="B536" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C536" s="4" t="s">
@@ -17087,7 +17093,7 @@
     </row>
     <row r="537" spans="2:7" ht="15.75" customHeight="1">
       <c r="B537" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C537" s="4" t="s">
@@ -17108,7 +17114,7 @@
     </row>
     <row r="538" spans="2:7" ht="15.75" customHeight="1">
       <c r="B538" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C538" s="4" t="s">
@@ -17129,7 +17135,7 @@
     </row>
     <row r="539" spans="2:7" ht="15.75" customHeight="1">
       <c r="B539" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C539" s="4" t="s">
@@ -17150,7 +17156,7 @@
     </row>
     <row r="540" spans="2:7" ht="15.75" customHeight="1">
       <c r="B540" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C540" s="4" t="s">
@@ -17171,7 +17177,7 @@
     </row>
     <row r="541" spans="2:7" ht="15.75" customHeight="1">
       <c r="B541" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C541" s="4" t="s">
@@ -17192,7 +17198,7 @@
     </row>
     <row r="542" spans="2:7" ht="15.75" customHeight="1">
       <c r="B542" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C542" s="4" t="s">
@@ -17213,7 +17219,7 @@
     </row>
     <row r="543" spans="2:7" ht="15.75" customHeight="1">
       <c r="B543" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C543" s="4" t="s">
@@ -17234,7 +17240,7 @@
     </row>
     <row r="544" spans="2:7" ht="15.75" customHeight="1">
       <c r="B544" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C544" s="4" t="s">
@@ -17255,7 +17261,7 @@
     </row>
     <row r="545" spans="2:7" ht="15.75" customHeight="1">
       <c r="B545" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C545" s="4" t="s">
@@ -17276,7 +17282,7 @@
     </row>
     <row r="546" spans="2:7" ht="15.75" customHeight="1">
       <c r="B546" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C546" s="4" t="s">
@@ -17297,7 +17303,7 @@
     </row>
     <row r="547" spans="2:7" ht="15.75" customHeight="1">
       <c r="B547" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C547" s="4" t="s">
@@ -17318,7 +17324,7 @@
     </row>
     <row r="548" spans="2:7" ht="15.75" customHeight="1">
       <c r="B548" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C548" s="4" t="s">
@@ -17339,7 +17345,7 @@
     </row>
     <row r="549" spans="2:7" ht="15.75" customHeight="1">
       <c r="B549" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C549" s="4" t="s">
@@ -17360,7 +17366,7 @@
     </row>
     <row r="550" spans="2:7" ht="15.75" customHeight="1">
       <c r="B550" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C550" s="4" t="s">
@@ -17381,7 +17387,7 @@
     </row>
     <row r="551" spans="2:7" ht="15.75" customHeight="1">
       <c r="B551" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C551" s="4" t="s">
@@ -17402,7 +17408,7 @@
     </row>
     <row r="552" spans="2:7" ht="15.75" customHeight="1">
       <c r="B552" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C552" s="4" t="s">
@@ -17423,7 +17429,7 @@
     </row>
     <row r="553" spans="2:7" ht="15.75" customHeight="1">
       <c r="B553" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C553" s="4" t="s">
@@ -17444,7 +17450,7 @@
     </row>
     <row r="554" spans="2:7" ht="15.75" customHeight="1">
       <c r="B554" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C554" s="4" t="s">
@@ -17465,7 +17471,7 @@
     </row>
     <row r="555" spans="2:7" ht="15.75" customHeight="1">
       <c r="B555" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C555" s="4" t="s">
@@ -17486,7 +17492,7 @@
     </row>
     <row r="556" spans="2:7" ht="15.75" customHeight="1">
       <c r="B556" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C556" s="4" t="s">
@@ -17507,7 +17513,7 @@
     </row>
     <row r="557" spans="2:7" ht="15.75" customHeight="1">
       <c r="B557" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C557" s="4" t="s">
@@ -17528,7 +17534,7 @@
     </row>
     <row r="558" spans="2:7" ht="15.75" customHeight="1">
       <c r="B558" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C558" s="4" t="s">
@@ -17549,7 +17555,7 @@
     </row>
     <row r="559" spans="2:7" ht="15.75" customHeight="1">
       <c r="B559" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C559" s="4" t="s">
@@ -17570,7 +17576,7 @@
     </row>
     <row r="560" spans="2:7" ht="15.75" customHeight="1">
       <c r="B560" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C560" s="4" t="s">
@@ -17591,7 +17597,7 @@
     </row>
     <row r="561" spans="2:7" ht="15.75" customHeight="1">
       <c r="B561" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C561" s="4" t="s">
@@ -17612,7 +17618,7 @@
     </row>
     <row r="562" spans="2:7" ht="15.75" customHeight="1">
       <c r="B562" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C562" s="4" t="s">
@@ -17633,7 +17639,7 @@
     </row>
     <row r="563" spans="2:7" ht="15.75" customHeight="1">
       <c r="B563" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C563" s="4" t="s">
@@ -17654,7 +17660,7 @@
     </row>
     <row r="564" spans="2:7" ht="15.75" customHeight="1">
       <c r="B564" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C564" s="4" t="s">
@@ -17675,7 +17681,7 @@
     </row>
     <row r="565" spans="2:7" ht="15.75" customHeight="1">
       <c r="B565" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C565" s="4" t="s">
@@ -17696,7 +17702,7 @@
     </row>
     <row r="566" spans="2:7" ht="15.75" customHeight="1">
       <c r="B566" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C566" s="4" t="s">
@@ -17717,7 +17723,7 @@
     </row>
     <row r="567" spans="2:7" ht="15.75" customHeight="1">
       <c r="B567" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
         <v>46161</v>
       </c>
       <c r="C567" s="4" t="s">
@@ -17758,7 +17764,7 @@
     </row>
     <row r="569" spans="2:7" ht="15.75" customHeight="1">
       <c r="B569" s="6">
-        <f t="shared" ref="B569:B576" si="42">B568</f>
+        <f t="shared" ref="B569:B576" si="33">B568</f>
         <v>46162</v>
       </c>
       <c r="C569" s="4" t="s">
@@ -17779,7 +17785,7 @@
     </row>
     <row r="570" spans="2:7" ht="15.75" customHeight="1">
       <c r="B570" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C570" s="4" t="s">
@@ -17800,7 +17806,7 @@
     </row>
     <row r="571" spans="2:7" ht="15.75" customHeight="1">
       <c r="B571" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C571" s="4" t="s">
@@ -17821,7 +17827,7 @@
     </row>
     <row r="572" spans="2:7" ht="15.75" customHeight="1">
       <c r="B572" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C572" s="4" t="s">
@@ -17842,7 +17848,7 @@
     </row>
     <row r="573" spans="2:7" ht="15.75" customHeight="1">
       <c r="B573" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C573" s="4" t="s">
@@ -17863,7 +17869,7 @@
     </row>
     <row r="574" spans="2:7" ht="15.75" customHeight="1">
       <c r="B574" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C574" s="4" t="s">
@@ -17884,7 +17890,7 @@
     </row>
     <row r="575" spans="2:7" ht="15.75" customHeight="1">
       <c r="B575" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C575" s="4" t="s">
@@ -17905,7 +17911,7 @@
     </row>
     <row r="576" spans="2:7" ht="15.75" customHeight="1">
       <c r="B576" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>46162</v>
       </c>
       <c r="C576" s="4" t="s">
@@ -17946,7 +17952,7 @@
     </row>
     <row r="578" spans="2:7" ht="15.75" customHeight="1">
       <c r="B578" s="6">
-        <f t="shared" ref="B578:B581" si="43">B577</f>
+        <f>B577</f>
         <v>46163</v>
       </c>
       <c r="C578" s="4" t="s">
@@ -17967,7 +17973,7 @@
     </row>
     <row r="579" spans="2:7" ht="15.75" customHeight="1">
       <c r="B579" s="6">
-        <f t="shared" si="43"/>
+        <f>B578</f>
         <v>46163</v>
       </c>
       <c r="C579" s="4" t="s">
@@ -17988,7 +17994,7 @@
     </row>
     <row r="580" spans="2:7" ht="15.75" customHeight="1">
       <c r="B580" s="6">
-        <f t="shared" si="43"/>
+        <f>B579</f>
         <v>46163</v>
       </c>
       <c r="C580" s="4" t="s">
@@ -18009,7 +18015,7 @@
     </row>
     <row r="581" spans="2:7" ht="15.75" customHeight="1">
       <c r="B581" s="6">
-        <f t="shared" si="43"/>
+        <f>B580</f>
         <v>46163</v>
       </c>
       <c r="C581" s="4" t="s">
@@ -18050,7 +18056,7 @@
     </row>
     <row r="583" spans="2:7" ht="15.75" customHeight="1">
       <c r="B583" s="6">
-        <f t="shared" ref="B583:B610" si="44">B582</f>
+        <f t="shared" ref="B583:B610" si="34">B582</f>
         <v>46164</v>
       </c>
       <c r="C583" s="4" t="s">
@@ -18071,7 +18077,7 @@
     </row>
     <row r="584" spans="2:7" ht="15.75" customHeight="1">
       <c r="B584" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C584" s="4" t="s">
@@ -18092,7 +18098,7 @@
     </row>
     <row r="585" spans="2:7" ht="15.75" customHeight="1">
       <c r="B585" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C585" s="4" t="s">
@@ -18113,7 +18119,7 @@
     </row>
     <row r="586" spans="2:7" ht="15.75" customHeight="1">
       <c r="B586" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C586" s="4" t="s">
@@ -18134,7 +18140,7 @@
     </row>
     <row r="587" spans="2:7" ht="15.75" customHeight="1">
       <c r="B587" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C587" s="4" t="s">
@@ -18155,7 +18161,7 @@
     </row>
     <row r="588" spans="2:7" ht="15.75" customHeight="1">
       <c r="B588" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C588" s="4" t="s">
@@ -18176,7 +18182,7 @@
     </row>
     <row r="589" spans="2:7" ht="15.75" customHeight="1">
       <c r="B589" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C589" s="4" t="s">
@@ -18197,7 +18203,7 @@
     </row>
     <row r="590" spans="2:7" ht="15.75" customHeight="1">
       <c r="B590" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C590" s="4" t="s">
@@ -18218,7 +18224,7 @@
     </row>
     <row r="591" spans="2:7" ht="15.75" customHeight="1">
       <c r="B591" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C591" s="4" t="s">
@@ -18239,7 +18245,7 @@
     </row>
     <row r="592" spans="2:7" ht="15.75" customHeight="1">
       <c r="B592" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C592" s="4" t="s">
@@ -18260,7 +18266,7 @@
     </row>
     <row r="593" spans="2:7" ht="15.75" customHeight="1">
       <c r="B593" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C593" s="4" t="s">
@@ -18281,7 +18287,7 @@
     </row>
     <row r="594" spans="2:7" ht="15.75" customHeight="1">
       <c r="B594" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C594" s="4" t="s">
@@ -18302,7 +18308,7 @@
     </row>
     <row r="595" spans="2:7" ht="15.75" customHeight="1">
       <c r="B595" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C595" s="4" t="s">
@@ -18323,7 +18329,7 @@
     </row>
     <row r="596" spans="2:7" ht="15.75" customHeight="1">
       <c r="B596" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C596" s="4" t="s">
@@ -18344,7 +18350,7 @@
     </row>
     <row r="597" spans="2:7" ht="15.75" customHeight="1">
       <c r="B597" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C597" s="4" t="s">
@@ -18365,7 +18371,7 @@
     </row>
     <row r="598" spans="2:7" ht="15.75" customHeight="1">
       <c r="B598" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C598" s="4" t="s">
@@ -18386,7 +18392,7 @@
     </row>
     <row r="599" spans="2:7" ht="15.75" customHeight="1">
       <c r="B599" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C599" s="4" t="s">
@@ -18407,7 +18413,7 @@
     </row>
     <row r="600" spans="2:7" ht="15.75" customHeight="1">
       <c r="B600" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C600" s="4" t="s">
@@ -18428,7 +18434,7 @@
     </row>
     <row r="601" spans="2:7" ht="15.75" customHeight="1">
       <c r="B601" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C601" s="4" t="s">
@@ -18449,7 +18455,7 @@
     </row>
     <row r="602" spans="2:7" ht="15.75" customHeight="1">
       <c r="B602" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C602" s="4" t="s">
@@ -18470,7 +18476,7 @@
     </row>
     <row r="603" spans="2:7" ht="15.75" customHeight="1">
       <c r="B603" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C603" s="4" t="s">
@@ -18491,7 +18497,7 @@
     </row>
     <row r="604" spans="2:7" ht="15.75" customHeight="1">
       <c r="B604" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C604" s="4" t="s">
@@ -18512,7 +18518,7 @@
     </row>
     <row r="605" spans="2:7" ht="15.75" customHeight="1">
       <c r="B605" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C605" s="4" t="s">
@@ -18533,7 +18539,7 @@
     </row>
     <row r="606" spans="2:7" ht="15.75" customHeight="1">
       <c r="B606" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C606" s="4" t="s">
@@ -18554,7 +18560,7 @@
     </row>
     <row r="607" spans="2:7" ht="15.75" customHeight="1">
       <c r="B607" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C607" s="4" t="s">
@@ -18575,7 +18581,7 @@
     </row>
     <row r="608" spans="2:7" ht="15.75" customHeight="1">
       <c r="B608" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C608" s="4" t="s">
@@ -18596,7 +18602,7 @@
     </row>
     <row r="609" spans="2:7" ht="15.75" customHeight="1">
       <c r="B609" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C609" s="4" t="s">
@@ -18617,7 +18623,7 @@
     </row>
     <row r="610" spans="2:7" ht="15.75" customHeight="1">
       <c r="B610" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="34"/>
         <v>46164</v>
       </c>
       <c r="C610" s="4" t="s">
@@ -18656,7 +18662,7 @@
     </row>
     <row r="612" spans="2:7" ht="15.75" customHeight="1">
       <c r="B612" s="6">
-        <f t="shared" ref="B612:B627" si="45">B611</f>
+        <f t="shared" ref="B612:B627" si="35">B611</f>
         <v>46165</v>
       </c>
       <c r="C612" s="4" t="s">
@@ -18677,7 +18683,7 @@
     </row>
     <row r="613" spans="2:7" ht="15.75" customHeight="1">
       <c r="B613" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C613" s="4" t="s">
@@ -18698,7 +18704,7 @@
     </row>
     <row r="614" spans="2:7" ht="15.75" customHeight="1">
       <c r="B614" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C614" s="4" t="s">
@@ -18719,7 +18725,7 @@
     </row>
     <row r="615" spans="2:7" ht="15.75" customHeight="1">
       <c r="B615" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C615" s="7" t="s">
@@ -18740,7 +18746,7 @@
     </row>
     <row r="616" spans="2:7" ht="15.75" customHeight="1">
       <c r="B616" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C616" s="4" t="s">
@@ -18761,7 +18767,7 @@
     </row>
     <row r="617" spans="2:7" ht="15.75" customHeight="1">
       <c r="B617" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C617" s="4" t="s">
@@ -18782,7 +18788,7 @@
     </row>
     <row r="618" spans="2:7" ht="15.75" customHeight="1">
       <c r="B618" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C618" s="4" t="s">
@@ -18803,7 +18809,7 @@
     </row>
     <row r="619" spans="2:7" ht="15.75" customHeight="1">
       <c r="B619" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C619" s="4" t="s">
@@ -18824,7 +18830,7 @@
     </row>
     <row r="620" spans="2:7" ht="15.75" customHeight="1">
       <c r="B620" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C620" s="4" t="s">
@@ -18845,7 +18851,7 @@
     </row>
     <row r="621" spans="2:7" ht="15.75" customHeight="1">
       <c r="B621" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C621" s="4" t="s">
@@ -18866,7 +18872,7 @@
     </row>
     <row r="622" spans="2:7" ht="15.75" customHeight="1">
       <c r="B622" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C622" s="4" t="s">
@@ -18887,7 +18893,7 @@
     </row>
     <row r="623" spans="2:7" ht="15.75" customHeight="1">
       <c r="B623" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C623" s="4" t="s">
@@ -18908,7 +18914,7 @@
     </row>
     <row r="624" spans="2:7" ht="15.75" customHeight="1">
       <c r="B624" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C624" s="4" t="s">
@@ -18929,7 +18935,7 @@
     </row>
     <row r="625" spans="2:7" ht="15.75" customHeight="1">
       <c r="B625" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C625" s="4" t="s">
@@ -18950,7 +18956,7 @@
     </row>
     <row r="626" spans="2:7" ht="15.75" customHeight="1">
       <c r="B626" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C626" s="4" t="s">
@@ -18971,7 +18977,7 @@
     </row>
     <row r="627" spans="2:7" ht="15.75" customHeight="1">
       <c r="B627" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="35"/>
         <v>46165</v>
       </c>
       <c r="C627" s="4" t="s">
@@ -19012,7 +19018,7 @@
     </row>
     <row r="629" spans="2:7" ht="15.75" customHeight="1">
       <c r="B629" s="6">
-        <f t="shared" ref="B629:B654" si="46">B628</f>
+        <f t="shared" ref="B629:B654" si="36">B628</f>
         <v>46166</v>
       </c>
       <c r="C629" s="7" t="s">
@@ -19033,7 +19039,7 @@
     </row>
     <row r="630" spans="2:7" ht="15.75" customHeight="1">
       <c r="B630" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C630" s="4" t="s">
@@ -19054,7 +19060,7 @@
     </row>
     <row r="631" spans="2:7" ht="15.75" customHeight="1">
       <c r="B631" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C631" s="4" t="s">
@@ -19075,7 +19081,7 @@
     </row>
     <row r="632" spans="2:7" ht="15.75" customHeight="1">
       <c r="B632" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C632" s="7" t="s">
@@ -19096,7 +19102,7 @@
     </row>
     <row r="633" spans="2:7" ht="15.75" customHeight="1">
       <c r="B633" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C633" s="7" t="s">
@@ -19117,7 +19123,7 @@
     </row>
     <row r="634" spans="2:7" ht="15.75" customHeight="1">
       <c r="B634" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C634" s="4" t="s">
@@ -19138,7 +19144,7 @@
     </row>
     <row r="635" spans="2:7" ht="15.75" customHeight="1">
       <c r="B635" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C635" s="4" t="s">
@@ -19159,7 +19165,7 @@
     </row>
     <row r="636" spans="2:7" ht="15.75" customHeight="1">
       <c r="B636" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C636" s="4" t="s">
@@ -19180,7 +19186,7 @@
     </row>
     <row r="637" spans="2:7" ht="15.75" customHeight="1">
       <c r="B637" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C637" s="4" t="s">
@@ -19201,7 +19207,7 @@
     </row>
     <row r="638" spans="2:7" ht="15.75" customHeight="1">
       <c r="B638" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C638" s="4" t="s">
@@ -19222,7 +19228,7 @@
     </row>
     <row r="639" spans="2:7" ht="15.75" customHeight="1">
       <c r="B639" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C639" s="4" t="s">
@@ -19243,7 +19249,7 @@
     </row>
     <row r="640" spans="2:7" ht="15.75" customHeight="1">
       <c r="B640" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C640" s="4" t="s">
@@ -19264,7 +19270,7 @@
     </row>
     <row r="641" spans="2:7" ht="15.75" customHeight="1">
       <c r="B641" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C641" s="4" t="s">
@@ -19285,7 +19291,7 @@
     </row>
     <row r="642" spans="2:7" ht="15.75" customHeight="1">
       <c r="B642" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C642" s="4" t="s">
@@ -19306,7 +19312,7 @@
     </row>
     <row r="643" spans="2:7" ht="15.75" customHeight="1">
       <c r="B643" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C643" s="4" t="s">
@@ -19327,7 +19333,7 @@
     </row>
     <row r="644" spans="2:7" ht="15.75" customHeight="1">
       <c r="B644" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C644" s="4" t="s">
@@ -19348,7 +19354,7 @@
     </row>
     <row r="645" spans="2:7" ht="15.75" customHeight="1">
       <c r="B645" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C645" s="4" t="s">
@@ -19369,7 +19375,7 @@
     </row>
     <row r="646" spans="2:7" ht="15.75" customHeight="1">
       <c r="B646" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C646" s="4" t="s">
@@ -19390,7 +19396,7 @@
     </row>
     <row r="647" spans="2:7" ht="15.75" customHeight="1">
       <c r="B647" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C647" s="4" t="s">
@@ -19411,7 +19417,7 @@
     </row>
     <row r="648" spans="2:7" ht="15.75" customHeight="1">
       <c r="B648" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C648" s="4" t="s">
@@ -19432,7 +19438,7 @@
     </row>
     <row r="649" spans="2:7" ht="15.75" customHeight="1">
       <c r="B649" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C649" s="4" t="s">
@@ -19453,7 +19459,7 @@
     </row>
     <row r="650" spans="2:7" ht="15.75" customHeight="1">
       <c r="B650" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C650" s="4" t="s">
@@ -19474,7 +19480,7 @@
     </row>
     <row r="651" spans="2:7" ht="15.75" customHeight="1">
       <c r="B651" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C651" s="4" t="s">
@@ -19495,7 +19501,7 @@
     </row>
     <row r="652" spans="2:7" ht="15.75" customHeight="1">
       <c r="B652" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C652" s="4" t="s">
@@ -19516,7 +19522,7 @@
     </row>
     <row r="653" spans="2:7" ht="15.75" customHeight="1">
       <c r="B653" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C653" s="4" t="s">
@@ -19537,7 +19543,7 @@
     </row>
     <row r="654" spans="2:7" ht="15.75" customHeight="1">
       <c r="B654" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>46166</v>
       </c>
       <c r="C654" s="4" t="s">
@@ -19578,7 +19584,7 @@
     </row>
     <row r="656" spans="2:7" ht="15.75" customHeight="1">
       <c r="B656" s="6">
-        <f t="shared" ref="B656:B672" si="47">B655</f>
+        <f t="shared" ref="B656:B672" si="37">B655</f>
         <v>46167</v>
       </c>
       <c r="C656" s="4" t="s">
@@ -19599,7 +19605,7 @@
     </row>
     <row r="657" spans="2:7" ht="15.75" customHeight="1">
       <c r="B657" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C657" s="4" t="s">
@@ -19620,7 +19626,7 @@
     </row>
     <row r="658" spans="2:7" ht="15.75" customHeight="1">
       <c r="B658" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C658" s="4" t="s">
@@ -19641,7 +19647,7 @@
     </row>
     <row r="659" spans="2:7" ht="15.75" customHeight="1">
       <c r="B659" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C659" s="4" t="s">
@@ -19662,7 +19668,7 @@
     </row>
     <row r="660" spans="2:7" ht="15.75" customHeight="1">
       <c r="B660" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C660" s="9" t="s">
@@ -19683,7 +19689,7 @@
     </row>
     <row r="661" spans="2:7" ht="15.75" customHeight="1">
       <c r="B661" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C661" s="9" t="s">
@@ -19704,7 +19710,7 @@
     </row>
     <row r="662" spans="2:7" ht="15.75" customHeight="1">
       <c r="B662" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C662" s="9" t="s">
@@ -19725,7 +19731,7 @@
     </row>
     <row r="663" spans="2:7" ht="15.75" customHeight="1">
       <c r="B663" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C663" s="9" t="s">
@@ -19746,7 +19752,7 @@
     </row>
     <row r="664" spans="2:7" ht="15.75" customHeight="1">
       <c r="B664" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C664" s="4" t="s">
@@ -19767,7 +19773,7 @@
     </row>
     <row r="665" spans="2:7" ht="15.75" customHeight="1">
       <c r="B665" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C665" s="4" t="s">
@@ -19788,7 +19794,7 @@
     </row>
     <row r="666" spans="2:7" ht="15.75" customHeight="1">
       <c r="B666" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C666" s="4" t="s">
@@ -19809,7 +19815,7 @@
     </row>
     <row r="667" spans="2:7" ht="15.75" customHeight="1">
       <c r="B667" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C667" s="4" t="s">
@@ -19830,7 +19836,7 @@
     </row>
     <row r="668" spans="2:7" ht="15.75" customHeight="1">
       <c r="B668" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C668" s="4" t="s">
@@ -19851,7 +19857,7 @@
     </row>
     <row r="669" spans="2:7" ht="15.75" customHeight="1">
       <c r="B669" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C669" s="4" t="s">
@@ -19872,7 +19878,7 @@
     </row>
     <row r="670" spans="2:7" ht="15.75" customHeight="1">
       <c r="B670" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C670" s="4" t="s">
@@ -19893,7 +19899,7 @@
     </row>
     <row r="671" spans="2:7" ht="15.75" customHeight="1">
       <c r="B671" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C671" s="4" t="s">
@@ -19914,7 +19920,7 @@
     </row>
     <row r="672" spans="2:7" ht="15.75" customHeight="1">
       <c r="B672" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="37"/>
         <v>46167</v>
       </c>
       <c r="C672" s="4" t="s">
@@ -19955,7 +19961,7 @@
     </row>
     <row r="674" spans="2:7" ht="15.75" customHeight="1">
       <c r="B674" s="6">
-        <f t="shared" ref="B674:B675" si="48">B673</f>
+        <f>B673</f>
         <v>46168</v>
       </c>
       <c r="C674" s="4" t="s">
@@ -19976,7 +19982,7 @@
     </row>
     <row r="675" spans="2:7" ht="15.75" customHeight="1">
       <c r="B675" s="6">
-        <f t="shared" si="48"/>
+        <f>B674</f>
         <v>46168</v>
       </c>
       <c r="C675" s="4" t="s">
@@ -20017,7 +20023,7 @@
     </row>
     <row r="677" spans="2:7" ht="15.75" customHeight="1">
       <c r="B677" s="6">
-        <f t="shared" ref="B677:B693" si="49">B676</f>
+        <f t="shared" ref="B677:B693" si="38">B676</f>
         <v>46169</v>
       </c>
       <c r="C677" s="4" t="s">
@@ -20038,7 +20044,7 @@
     </row>
     <row r="678" spans="2:7" ht="15.75" customHeight="1">
       <c r="B678" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C678" s="8" t="s">
@@ -20059,7 +20065,7 @@
     </row>
     <row r="679" spans="2:7" ht="15.75" customHeight="1">
       <c r="B679" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C679" s="8" t="s">
@@ -20080,7 +20086,7 @@
     </row>
     <row r="680" spans="2:7" ht="15.75" customHeight="1">
       <c r="B680" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C680" s="8" t="s">
@@ -20101,7 +20107,7 @@
     </row>
     <row r="681" spans="2:7" ht="15.75" customHeight="1">
       <c r="B681" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C681" s="8" t="s">
@@ -20122,7 +20128,7 @@
     </row>
     <row r="682" spans="2:7" ht="15.75" customHeight="1">
       <c r="B682" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C682" s="8" t="s">
@@ -20143,7 +20149,7 @@
     </row>
     <row r="683" spans="2:7" ht="15.75" customHeight="1">
       <c r="B683" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C683" s="8" t="s">
@@ -20164,7 +20170,7 @@
     </row>
     <row r="684" spans="2:7" ht="15.75" customHeight="1">
       <c r="B684" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C684" s="8" t="s">
@@ -20185,7 +20191,7 @@
     </row>
     <row r="685" spans="2:7" ht="15.75" customHeight="1">
       <c r="B685" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C685" s="8" t="s">
@@ -20206,7 +20212,7 @@
     </row>
     <row r="686" spans="2:7" ht="15.75" customHeight="1">
       <c r="B686" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C686" s="8" t="s">
@@ -20227,7 +20233,7 @@
     </row>
     <row r="687" spans="2:7" ht="15.75" customHeight="1">
       <c r="B687" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C687" s="8" t="s">
@@ -20248,7 +20254,7 @@
     </row>
     <row r="688" spans="2:7" ht="15.75" customHeight="1">
       <c r="B688" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C688" s="8" t="s">
@@ -20269,7 +20275,7 @@
     </row>
     <row r="689" spans="2:7" ht="15.75" customHeight="1">
       <c r="B689" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C689" s="8" t="s">
@@ -20290,7 +20296,7 @@
     </row>
     <row r="690" spans="2:7" ht="15.75" customHeight="1">
       <c r="B690" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C690" s="4" t="s">
@@ -20311,7 +20317,7 @@
     </row>
     <row r="691" spans="2:7" ht="15.75" customHeight="1">
       <c r="B691" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C691" s="4" t="s">
@@ -20332,7 +20338,7 @@
     </row>
     <row r="692" spans="2:7" ht="15.75" customHeight="1">
       <c r="B692" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C692" s="4" t="s">
@@ -20353,7 +20359,7 @@
     </row>
     <row r="693" spans="2:7" ht="15.75" customHeight="1">
       <c r="B693" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="38"/>
         <v>46169</v>
       </c>
       <c r="C693" s="4" t="s">
@@ -20394,7 +20400,7 @@
     </row>
     <row r="695" spans="2:7" ht="15.75" customHeight="1">
       <c r="B695" s="6">
-        <f t="shared" ref="B695:B715" si="50">B694</f>
+        <f t="shared" ref="B695:B715" si="39">B694</f>
         <v>46170</v>
       </c>
       <c r="C695" s="4" t="s">
@@ -20415,7 +20421,7 @@
     </row>
     <row r="696" spans="2:7" ht="15.75" customHeight="1">
       <c r="B696" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C696" s="4" t="s">
@@ -20436,7 +20442,7 @@
     </row>
     <row r="697" spans="2:7" ht="15.75" customHeight="1">
       <c r="B697" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C697" s="4" t="s">
@@ -20457,7 +20463,7 @@
     </row>
     <row r="698" spans="2:7" ht="15.75" customHeight="1">
       <c r="B698" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C698" s="4" t="s">
@@ -20478,7 +20484,7 @@
     </row>
     <row r="699" spans="2:7" ht="15.75" customHeight="1">
       <c r="B699" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C699" s="4" t="s">
@@ -20499,7 +20505,7 @@
     </row>
     <row r="700" spans="2:7" ht="15.75" customHeight="1">
       <c r="B700" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C700" s="4" t="s">
@@ -20520,7 +20526,7 @@
     </row>
     <row r="701" spans="2:7" ht="15.75" customHeight="1">
       <c r="B701" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C701" s="4" t="s">
@@ -20541,7 +20547,7 @@
     </row>
     <row r="702" spans="2:7" ht="15.75" customHeight="1">
       <c r="B702" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C702" s="4" t="s">
@@ -20562,7 +20568,7 @@
     </row>
     <row r="703" spans="2:7" ht="15.75" customHeight="1">
       <c r="B703" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C703" s="4" t="s">
@@ -20583,7 +20589,7 @@
     </row>
     <row r="704" spans="2:7" ht="15.75" customHeight="1">
       <c r="B704" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C704" s="4" t="s">
@@ -20604,7 +20610,7 @@
     </row>
     <row r="705" spans="2:7" ht="15.75" customHeight="1">
       <c r="B705" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C705" s="4" t="s">
@@ -20625,7 +20631,7 @@
     </row>
     <row r="706" spans="2:7" ht="15.75" customHeight="1">
       <c r="B706" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C706" s="4" t="s">
@@ -20646,7 +20652,7 @@
     </row>
     <row r="707" spans="2:7" ht="15.75" customHeight="1">
       <c r="B707" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C707" s="4" t="s">
@@ -20667,7 +20673,7 @@
     </row>
     <row r="708" spans="2:7" ht="15.75" customHeight="1">
       <c r="B708" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C708" s="4" t="s">
@@ -20688,7 +20694,7 @@
     </row>
     <row r="709" spans="2:7" ht="15.75" customHeight="1">
       <c r="B709" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C709" s="4" t="s">
@@ -20709,7 +20715,7 @@
     </row>
     <row r="710" spans="2:7" ht="15.75" customHeight="1">
       <c r="B710" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C710" s="4" t="s">
@@ -20730,7 +20736,7 @@
     </row>
     <row r="711" spans="2:7" ht="15.75" customHeight="1">
       <c r="B711" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C711" s="4" t="s">
@@ -20751,7 +20757,7 @@
     </row>
     <row r="712" spans="2:7" ht="15.75" customHeight="1">
       <c r="B712" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C712" s="4" t="s">
@@ -20772,7 +20778,7 @@
     </row>
     <row r="713" spans="2:7" ht="15.75" customHeight="1">
       <c r="B713" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C713" s="4" t="s">
@@ -20793,7 +20799,7 @@
     </row>
     <row r="714" spans="2:7" ht="15.75" customHeight="1">
       <c r="B714" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C714" s="4" t="s">
@@ -20814,7 +20820,7 @@
     </row>
     <row r="715" spans="2:7" ht="15.75" customHeight="1">
       <c r="B715" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="39"/>
         <v>46170</v>
       </c>
       <c r="C715" s="4" t="s">
@@ -20855,7 +20861,7 @@
     </row>
     <row r="717" spans="2:7" ht="15.75" customHeight="1">
       <c r="B717" s="6">
-        <f t="shared" ref="B717:B722" si="51">B716</f>
+        <f t="shared" ref="B717:B722" si="40">B716</f>
         <v>46171</v>
       </c>
       <c r="C717" s="4" t="s">
@@ -20876,7 +20882,7 @@
     </row>
     <row r="718" spans="2:7" ht="15.75" customHeight="1">
       <c r="B718" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="40"/>
         <v>46171</v>
       </c>
       <c r="C718" s="4" t="s">
@@ -20897,7 +20903,7 @@
     </row>
     <row r="719" spans="2:7" ht="15.75" customHeight="1">
       <c r="B719" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="40"/>
         <v>46171</v>
       </c>
       <c r="C719" s="4" t="s">
@@ -20918,7 +20924,7 @@
     </row>
     <row r="720" spans="2:7" ht="15.75" customHeight="1">
       <c r="B720" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="40"/>
         <v>46171</v>
       </c>
       <c r="C720" s="4" t="s">
@@ -20939,7 +20945,7 @@
     </row>
     <row r="721" spans="2:7" ht="15.75" customHeight="1">
       <c r="B721" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="40"/>
         <v>46171</v>
       </c>
       <c r="C721" s="4" t="s">
@@ -20960,7 +20966,7 @@
     </row>
     <row r="722" spans="2:7" ht="15.75" customHeight="1">
       <c r="B722" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="40"/>
         <v>46171</v>
       </c>
       <c r="C722" s="4" t="s">
@@ -21001,7 +21007,7 @@
     </row>
     <row r="724" spans="2:7" ht="15.75" customHeight="1">
       <c r="B724" s="6">
-        <f t="shared" ref="B724:B730" si="52">B723</f>
+        <f t="shared" ref="B724:B730" si="41">B723</f>
         <v>46172</v>
       </c>
       <c r="C724" s="4" t="s">
@@ -21022,7 +21028,7 @@
     </row>
     <row r="725" spans="2:7" ht="15.75" customHeight="1">
       <c r="B725" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C725" s="4" t="s">
@@ -21041,7 +21047,7 @@
     </row>
     <row r="726" spans="2:7" ht="15.75" customHeight="1">
       <c r="B726" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C726" s="4" t="s">
@@ -21062,7 +21068,7 @@
     </row>
     <row r="727" spans="2:7" ht="15.75" customHeight="1">
       <c r="B727" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C727" s="4" t="s">
@@ -21083,7 +21089,7 @@
     </row>
     <row r="728" spans="2:7" ht="15.75" customHeight="1">
       <c r="B728" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C728" s="4" t="s">
@@ -21104,7 +21110,7 @@
     </row>
     <row r="729" spans="2:7" ht="15.75" customHeight="1">
       <c r="B729" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C729" s="4" t="s">
@@ -21125,7 +21131,7 @@
     </row>
     <row r="730" spans="2:7" ht="15.75" customHeight="1">
       <c r="B730" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>46172</v>
       </c>
       <c r="C730" s="4" t="s">
@@ -21166,7 +21172,7 @@
     </row>
     <row r="732" spans="2:7" ht="15.75" customHeight="1">
       <c r="B732" s="6">
-        <f t="shared" ref="B732:B753" si="53">B731</f>
+        <f t="shared" ref="B732:B753" si="42">B731</f>
         <v>46173</v>
       </c>
       <c r="C732" s="4" t="s">
@@ -21187,7 +21193,7 @@
     </row>
     <row r="733" spans="2:7" ht="15.75" customHeight="1">
       <c r="B733" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C733" s="4" t="s">
@@ -21208,7 +21214,7 @@
     </row>
     <row r="734" spans="2:7" ht="15.75" customHeight="1">
       <c r="B734" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C734" s="4" t="s">
@@ -21229,7 +21235,7 @@
     </row>
     <row r="735" spans="2:7" ht="15.75" customHeight="1">
       <c r="B735" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C735" s="4" t="s">
@@ -21250,7 +21256,7 @@
     </row>
     <row r="736" spans="2:7" ht="15.75" customHeight="1">
       <c r="B736" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C736" s="4" t="s">
@@ -21271,7 +21277,7 @@
     </row>
     <row r="737" spans="2:7" ht="15.75" customHeight="1">
       <c r="B737" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C737" s="4" t="s">
@@ -21292,7 +21298,7 @@
     </row>
     <row r="738" spans="2:7" ht="15.75" customHeight="1">
       <c r="B738" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C738" s="4" t="s">
@@ -21313,7 +21319,7 @@
     </row>
     <row r="739" spans="2:7" ht="15.75" customHeight="1">
       <c r="B739" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C739" s="4" t="s">
@@ -21334,7 +21340,7 @@
     </row>
     <row r="740" spans="2:7" ht="15.75" customHeight="1">
       <c r="B740" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C740" s="4" t="s">
@@ -21355,7 +21361,7 @@
     </row>
     <row r="741" spans="2:7" ht="15.75" customHeight="1">
       <c r="B741" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C741" s="4" t="s">
@@ -21376,7 +21382,7 @@
     </row>
     <row r="742" spans="2:7" ht="15.75" customHeight="1">
       <c r="B742" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C742" s="4" t="s">
@@ -21397,7 +21403,7 @@
     </row>
     <row r="743" spans="2:7" ht="15.75" customHeight="1">
       <c r="B743" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C743" s="4" t="s">
@@ -21418,7 +21424,7 @@
     </row>
     <row r="744" spans="2:7" ht="15.75" customHeight="1">
       <c r="B744" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C744" s="4" t="s">
@@ -21439,7 +21445,7 @@
     </row>
     <row r="745" spans="2:7" ht="15.75" customHeight="1">
       <c r="B745" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C745" s="4" t="s">
@@ -21460,7 +21466,7 @@
     </row>
     <row r="746" spans="2:7" ht="15.75" customHeight="1">
       <c r="B746" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C746" s="4" t="s">
@@ -21481,7 +21487,7 @@
     </row>
     <row r="747" spans="2:7" ht="15.75" customHeight="1">
       <c r="B747" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C747" s="4" t="s">
@@ -21502,7 +21508,7 @@
     </row>
     <row r="748" spans="2:7" ht="15.75" customHeight="1">
       <c r="B748" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C748" s="4" t="s">
@@ -21523,7 +21529,7 @@
     </row>
     <row r="749" spans="2:7" ht="15.75" customHeight="1">
       <c r="B749" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C749" s="4" t="s">
@@ -21544,7 +21550,7 @@
     </row>
     <row r="750" spans="2:7" ht="15.75" customHeight="1">
       <c r="B750" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C750" s="4" t="s">
@@ -21565,7 +21571,7 @@
     </row>
     <row r="751" spans="2:7" ht="15.75" customHeight="1">
       <c r="B751" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C751" s="7" t="s">
@@ -21586,7 +21592,7 @@
     </row>
     <row r="752" spans="2:7" ht="15.75" customHeight="1">
       <c r="B752" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C752" s="7" t="s">
@@ -21607,7 +21613,7 @@
     </row>
     <row r="753" spans="2:7" ht="15.75" customHeight="1">
       <c r="B753" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>46173</v>
       </c>
       <c r="C753" s="7" t="s">
@@ -21648,7 +21654,7 @@
     </row>
     <row r="755" spans="2:7" ht="15.75" customHeight="1">
       <c r="B755" s="6">
-        <f t="shared" ref="B755:B767" si="54">B754</f>
+        <f t="shared" ref="B755:B767" si="43">B754</f>
         <v>46174</v>
       </c>
       <c r="C755" s="4" t="s">
@@ -21669,7 +21675,7 @@
     </row>
     <row r="756" spans="2:7" ht="15.75" customHeight="1">
       <c r="B756" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C756" s="4" t="s">
@@ -21690,7 +21696,7 @@
     </row>
     <row r="757" spans="2:7" ht="15.75" customHeight="1">
       <c r="B757" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C757" s="4" t="s">
@@ -21711,7 +21717,7 @@
     </row>
     <row r="758" spans="2:7" ht="15.75" customHeight="1">
       <c r="B758" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C758" s="4" t="s">
@@ -21732,7 +21738,7 @@
     </row>
     <row r="759" spans="2:7" ht="15.75" customHeight="1">
       <c r="B759" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C759" s="4" t="s">
@@ -21753,7 +21759,7 @@
     </row>
     <row r="760" spans="2:7" ht="15.75" customHeight="1">
       <c r="B760" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C760" s="4" t="s">
@@ -21774,7 +21780,7 @@
     </row>
     <row r="761" spans="2:7" ht="15.75" customHeight="1">
       <c r="B761" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C761" s="4" t="s">
@@ -21795,7 +21801,7 @@
     </row>
     <row r="762" spans="2:7" ht="15.75" customHeight="1">
       <c r="B762" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C762" s="4" t="s">
@@ -21816,7 +21822,7 @@
     </row>
     <row r="763" spans="2:7" ht="15.75" customHeight="1">
       <c r="B763" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C763" s="4" t="s">
@@ -21837,7 +21843,7 @@
     </row>
     <row r="764" spans="2:7" ht="15.75" customHeight="1">
       <c r="B764" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C764" s="4" t="s">
@@ -21858,7 +21864,7 @@
     </row>
     <row r="765" spans="2:7" ht="15.75" customHeight="1">
       <c r="B765" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C765" s="4" t="s">
@@ -21879,7 +21885,7 @@
     </row>
     <row r="766" spans="2:7" ht="15.75" customHeight="1">
       <c r="B766" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C766" s="4" t="s">
@@ -21900,7 +21906,7 @@
     </row>
     <row r="767" spans="2:7" ht="15.75" customHeight="1">
       <c r="B767" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="43"/>
         <v>46174</v>
       </c>
       <c r="C767" s="4" t="s">
@@ -21941,7 +21947,7 @@
     </row>
     <row r="769" spans="2:7" ht="15.75" customHeight="1">
       <c r="B769" s="6">
-        <f t="shared" ref="B769:B774" si="55">B768</f>
+        <f t="shared" ref="B769:B774" si="44">B768</f>
         <v>46175</v>
       </c>
       <c r="C769" s="4" t="s">
@@ -21962,7 +21968,7 @@
     </row>
     <row r="770" spans="2:7" ht="15.75" customHeight="1">
       <c r="B770" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="44"/>
         <v>46175</v>
       </c>
       <c r="C770" s="4" t="s">
@@ -21983,7 +21989,7 @@
     </row>
     <row r="771" spans="2:7" ht="15.75" customHeight="1">
       <c r="B771" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="44"/>
         <v>46175</v>
       </c>
       <c r="C771" s="4" t="s">
@@ -22004,7 +22010,7 @@
     </row>
     <row r="772" spans="2:7" ht="15.75" customHeight="1">
       <c r="B772" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="44"/>
         <v>46175</v>
       </c>
       <c r="C772" s="4" t="s">
@@ -22025,7 +22031,7 @@
     </row>
     <row r="773" spans="2:7" ht="15.75" customHeight="1">
       <c r="B773" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="44"/>
         <v>46175</v>
       </c>
       <c r="C773" s="4" t="s">
@@ -22046,7 +22052,7 @@
     </row>
     <row r="774" spans="2:7" ht="15.75" customHeight="1">
       <c r="B774" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="44"/>
         <v>46175</v>
       </c>
       <c r="C774" s="4" t="s">
@@ -22107,7 +22113,7 @@
     </row>
     <row r="777" spans="2:7" ht="15.75" customHeight="1">
       <c r="B777" s="6">
-        <f t="shared" ref="B777:B790" si="56">B776</f>
+        <f t="shared" ref="B777:B790" si="45">B776</f>
         <v>46177</v>
       </c>
       <c r="C777" s="4" t="s">
@@ -22128,7 +22134,7 @@
     </row>
     <row r="778" spans="2:7" ht="15.75" customHeight="1">
       <c r="B778" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C778" s="4" t="s">
@@ -22149,7 +22155,7 @@
     </row>
     <row r="779" spans="2:7" ht="15.75" customHeight="1">
       <c r="B779" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C779" s="4" t="s">
@@ -22170,7 +22176,7 @@
     </row>
     <row r="780" spans="2:7" ht="15.75" customHeight="1">
       <c r="B780" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C780" s="4" t="s">
@@ -22191,7 +22197,7 @@
     </row>
     <row r="781" spans="2:7" ht="15.75" customHeight="1">
       <c r="B781" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C781" s="4" t="s">
@@ -22212,7 +22218,7 @@
     </row>
     <row r="782" spans="2:7" ht="15.75" customHeight="1">
       <c r="B782" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C782" s="4" t="s">
@@ -22233,7 +22239,7 @@
     </row>
     <row r="783" spans="2:7" ht="15.75" customHeight="1">
       <c r="B783" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C783" s="4" t="s">
@@ -22254,7 +22260,7 @@
     </row>
     <row r="784" spans="2:7" ht="15.75" customHeight="1">
       <c r="B784" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C784" s="4" t="s">
@@ -22275,7 +22281,7 @@
     </row>
     <row r="785" spans="2:7" ht="15.75" customHeight="1">
       <c r="B785" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C785" s="4" t="s">
@@ -22296,7 +22302,7 @@
     </row>
     <row r="786" spans="2:7" ht="15.75" customHeight="1">
       <c r="B786" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C786" s="4" t="s">
@@ -22317,7 +22323,7 @@
     </row>
     <row r="787" spans="2:7" ht="15.75" customHeight="1">
       <c r="B787" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C787" s="4" t="s">
@@ -22338,7 +22344,7 @@
     </row>
     <row r="788" spans="2:7" ht="15.75" customHeight="1">
       <c r="B788" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C788" s="4" t="s">
@@ -22359,7 +22365,7 @@
     </row>
     <row r="789" spans="2:7" ht="15.75" customHeight="1">
       <c r="B789" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C789" s="4" t="s">
@@ -22380,7 +22386,7 @@
     </row>
     <row r="790" spans="2:7" ht="15.75" customHeight="1">
       <c r="B790" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="45"/>
         <v>46177</v>
       </c>
       <c r="C790" s="4" t="s">
@@ -22421,7 +22427,7 @@
     </row>
     <row r="792" spans="2:7" ht="15.75" customHeight="1">
       <c r="B792" s="6">
-        <f t="shared" ref="B792:B794" si="57">B791</f>
+        <f>B791</f>
         <v>46178</v>
       </c>
       <c r="C792" s="4" t="s">
@@ -22442,7 +22448,7 @@
     </row>
     <row r="793" spans="2:7" ht="15.75" customHeight="1">
       <c r="B793" s="6">
-        <f t="shared" si="57"/>
+        <f>B792</f>
         <v>46178</v>
       </c>
       <c r="C793" s="4" t="s">
@@ -22463,7 +22469,7 @@
     </row>
     <row r="794" spans="2:7" ht="15.75" customHeight="1">
       <c r="B794" s="6">
-        <f t="shared" si="57"/>
+        <f>B793</f>
         <v>46178</v>
       </c>
       <c r="C794" s="4" t="s">
@@ -22504,7 +22510,7 @@
     </row>
     <row r="796" spans="2:7" ht="15.75" customHeight="1">
       <c r="B796" s="6">
-        <f t="shared" ref="B796:B814" si="58">B795</f>
+        <f t="shared" ref="B796:B814" si="46">B795</f>
         <v>46179</v>
       </c>
       <c r="C796" s="4" t="s">
@@ -22525,7 +22531,7 @@
     </row>
     <row r="797" spans="2:7" ht="15.75" customHeight="1">
       <c r="B797" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C797" s="4" t="s">
@@ -22546,7 +22552,7 @@
     </row>
     <row r="798" spans="2:7" ht="15.75" customHeight="1">
       <c r="B798" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C798" s="4" t="s">
@@ -22567,7 +22573,7 @@
     </row>
     <row r="799" spans="2:7" ht="15.75" customHeight="1">
       <c r="B799" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C799" s="4" t="s">
@@ -22588,7 +22594,7 @@
     </row>
     <row r="800" spans="2:7" ht="15.75" customHeight="1">
       <c r="B800" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C800" s="4" t="s">
@@ -22609,7 +22615,7 @@
     </row>
     <row r="801" spans="2:7" ht="15.75" customHeight="1">
       <c r="B801" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C801" s="4" t="s">
@@ -22630,7 +22636,7 @@
     </row>
     <row r="802" spans="2:7" ht="15.75" customHeight="1">
       <c r="B802" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C802" s="4" t="s">
@@ -22651,7 +22657,7 @@
     </row>
     <row r="803" spans="2:7" ht="15.75" customHeight="1">
       <c r="B803" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C803" s="4" t="s">
@@ -22672,7 +22678,7 @@
     </row>
     <row r="804" spans="2:7" ht="15.75" customHeight="1">
       <c r="B804" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C804" s="4" t="s">
@@ -22693,7 +22699,7 @@
     </row>
     <row r="805" spans="2:7" ht="15.75" customHeight="1">
       <c r="B805" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C805" s="4" t="s">
@@ -22714,7 +22720,7 @@
     </row>
     <row r="806" spans="2:7" ht="15.75" customHeight="1">
       <c r="B806" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C806" s="4" t="s">
@@ -22735,7 +22741,7 @@
     </row>
     <row r="807" spans="2:7" ht="15.75" customHeight="1">
       <c r="B807" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C807" s="4" t="s">
@@ -22756,7 +22762,7 @@
     </row>
     <row r="808" spans="2:7" ht="15.75" customHeight="1">
       <c r="B808" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C808" s="4" t="s">
@@ -22777,7 +22783,7 @@
     </row>
     <row r="809" spans="2:7" ht="15.75" customHeight="1">
       <c r="B809" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C809" s="4" t="s">
@@ -22798,7 +22804,7 @@
     </row>
     <row r="810" spans="2:7" ht="15.75" customHeight="1">
       <c r="B810" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C810" s="4" t="s">
@@ -22819,7 +22825,7 @@
     </row>
     <row r="811" spans="2:7" ht="15.75" customHeight="1">
       <c r="B811" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C811" s="4" t="s">
@@ -22840,7 +22846,7 @@
     </row>
     <row r="812" spans="2:7" ht="15.75" customHeight="1">
       <c r="B812" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C812" s="4" t="s">
@@ -22861,7 +22867,7 @@
     </row>
     <row r="813" spans="2:7" ht="15.75" customHeight="1">
       <c r="B813" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C813" s="4" t="s">
@@ -22882,7 +22888,7 @@
     </row>
     <row r="814" spans="2:7" ht="15.75" customHeight="1">
       <c r="B814" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>46179</v>
       </c>
       <c r="C814" s="4" t="s">
@@ -22923,7 +22929,7 @@
     </row>
     <row r="816" spans="2:7" ht="15.75" customHeight="1">
       <c r="B816" s="6">
-        <f t="shared" ref="B816:B836" si="59">B815</f>
+        <f t="shared" ref="B816:B836" si="47">B815</f>
         <v>46180</v>
       </c>
       <c r="C816" s="4" t="s">
@@ -22944,7 +22950,7 @@
     </row>
     <row r="817" spans="2:7" ht="15.75" customHeight="1">
       <c r="B817" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C817" s="4" t="s">
@@ -22965,7 +22971,7 @@
     </row>
     <row r="818" spans="2:7" ht="15.75" customHeight="1">
       <c r="B818" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C818" s="4" t="s">
@@ -22986,7 +22992,7 @@
     </row>
     <row r="819" spans="2:7" ht="15.75" customHeight="1">
       <c r="B819" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C819" s="4" t="s">
@@ -23007,7 +23013,7 @@
     </row>
     <row r="820" spans="2:7" ht="15.75" customHeight="1">
       <c r="B820" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C820" s="4" t="s">
@@ -23028,7 +23034,7 @@
     </row>
     <row r="821" spans="2:7" ht="15.75" customHeight="1">
       <c r="B821" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C821" s="4" t="s">
@@ -23049,7 +23055,7 @@
     </row>
     <row r="822" spans="2:7" ht="15.75" customHeight="1">
       <c r="B822" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C822" s="4" t="s">
@@ -23070,7 +23076,7 @@
     </row>
     <row r="823" spans="2:7" ht="15.75" customHeight="1">
       <c r="B823" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C823" s="4" t="s">
@@ -23091,7 +23097,7 @@
     </row>
     <row r="824" spans="2:7" ht="15.75" customHeight="1">
       <c r="B824" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C824" s="4" t="s">
@@ -23112,7 +23118,7 @@
     </row>
     <row r="825" spans="2:7" ht="15.75" customHeight="1">
       <c r="B825" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C825" s="4" t="s">
@@ -23133,7 +23139,7 @@
     </row>
     <row r="826" spans="2:7" ht="15.75" customHeight="1">
       <c r="B826" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C826" s="4" t="s">
@@ -23154,7 +23160,7 @@
     </row>
     <row r="827" spans="2:7" ht="15.75" customHeight="1">
       <c r="B827" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C827" s="4" t="s">
@@ -23175,7 +23181,7 @@
     </row>
     <row r="828" spans="2:7" ht="15.75" customHeight="1">
       <c r="B828" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C828" s="4" t="s">
@@ -23196,7 +23202,7 @@
     </row>
     <row r="829" spans="2:7" ht="15.75" customHeight="1">
       <c r="B829" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C829" s="4" t="s">
@@ -23217,7 +23223,7 @@
     </row>
     <row r="830" spans="2:7" ht="15.75" customHeight="1">
       <c r="B830" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C830" s="4" t="s">
@@ -23238,7 +23244,7 @@
     </row>
     <row r="831" spans="2:7" ht="15.75" customHeight="1">
       <c r="B831" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C831" s="4" t="s">
@@ -23259,7 +23265,7 @@
     </row>
     <row r="832" spans="2:7" ht="15.75" customHeight="1">
       <c r="B832" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C832" s="4" t="s">
@@ -23280,7 +23286,7 @@
     </row>
     <row r="833" spans="2:7" ht="15.75" customHeight="1">
       <c r="B833" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C833" s="4" t="s">
@@ -23301,7 +23307,7 @@
     </row>
     <row r="834" spans="2:7" ht="15.75" customHeight="1">
       <c r="B834" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C834" s="4" t="s">
@@ -23322,7 +23328,7 @@
     </row>
     <row r="835" spans="2:7" ht="15.75" customHeight="1">
       <c r="B835" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C835" s="4" t="s">
@@ -23343,7 +23349,7 @@
     </row>
     <row r="836" spans="2:7" ht="15.75" customHeight="1">
       <c r="B836" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="47"/>
         <v>46180</v>
       </c>
       <c r="C836" s="4" t="s">
@@ -23384,7 +23390,7 @@
     </row>
     <row r="838" spans="2:7" ht="15.75" customHeight="1">
       <c r="B838" s="6">
-        <f t="shared" ref="B838:B844" si="60">B837</f>
+        <f t="shared" ref="B838:B844" si="48">B837</f>
         <v>46181</v>
       </c>
       <c r="C838" s="22" t="s">
@@ -23405,7 +23411,7 @@
     </row>
     <row r="839" spans="2:7" ht="15.75" customHeight="1">
       <c r="B839" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C839" s="22" t="s">
@@ -23426,7 +23432,7 @@
     </row>
     <row r="840" spans="2:7" ht="15.75" customHeight="1">
       <c r="B840" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C840" s="22" t="s">
@@ -23447,7 +23453,7 @@
     </row>
     <row r="841" spans="2:7" ht="15.75" customHeight="1">
       <c r="B841" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C841" s="22" t="s">
@@ -23468,7 +23474,7 @@
     </row>
     <row r="842" spans="2:7" ht="15.75" customHeight="1">
       <c r="B842" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C842" s="22" t="s">
@@ -23489,7 +23495,7 @@
     </row>
     <row r="843" spans="2:7" ht="15.75" customHeight="1">
       <c r="B843" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C843" s="22" t="s">
@@ -23510,7 +23516,7 @@
     </row>
     <row r="844" spans="2:7" ht="15.75" customHeight="1">
       <c r="B844" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>46181</v>
       </c>
       <c r="C844" s="22" t="s">
@@ -23551,7 +23557,7 @@
     </row>
     <row r="846" spans="2:7" ht="15.75" customHeight="1">
       <c r="B846" s="6">
-        <f t="shared" ref="B846:B847" si="61">B845</f>
+        <f>B845</f>
         <v>46151</v>
       </c>
       <c r="C846" s="4" t="s">
@@ -23572,7 +23578,7 @@
     </row>
     <row r="847" spans="2:7" ht="15.75" customHeight="1">
       <c r="B847" s="6">
-        <f t="shared" si="61"/>
+        <f>B846</f>
         <v>46151</v>
       </c>
       <c r="C847" s="4" t="s">
@@ -23613,7 +23619,7 @@
     </row>
     <row r="849" spans="2:7" ht="15.75" customHeight="1">
       <c r="B849" s="6">
-        <f t="shared" ref="B849:B884" si="62">B848</f>
+        <f t="shared" ref="B849:B884" si="49">B848</f>
         <v>46183</v>
       </c>
       <c r="C849" s="4" t="s">
@@ -23634,7 +23640,7 @@
     </row>
     <row r="850" spans="2:7" ht="15.75" customHeight="1">
       <c r="B850" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C850" s="4" t="s">
@@ -23655,7 +23661,7 @@
     </row>
     <row r="851" spans="2:7" ht="15.75" customHeight="1">
       <c r="B851" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C851" s="4" t="s">
@@ -23676,7 +23682,7 @@
     </row>
     <row r="852" spans="2:7" ht="15.75" customHeight="1">
       <c r="B852" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C852" s="4" t="s">
@@ -23697,7 +23703,7 @@
     </row>
     <row r="853" spans="2:7" ht="15.75" customHeight="1">
       <c r="B853" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C853" s="4" t="s">
@@ -23718,7 +23724,7 @@
     </row>
     <row r="854" spans="2:7" ht="15.75" customHeight="1">
       <c r="B854" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C854" s="4" t="s">
@@ -23739,7 +23745,7 @@
     </row>
     <row r="855" spans="2:7" ht="15.75" customHeight="1">
       <c r="B855" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C855" s="4" t="s">
@@ -23760,7 +23766,7 @@
     </row>
     <row r="856" spans="2:7" ht="15.75" customHeight="1">
       <c r="B856" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C856" s="4" t="s">
@@ -23781,7 +23787,7 @@
     </row>
     <row r="857" spans="2:7" ht="15.75" customHeight="1">
       <c r="B857" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C857" s="4" t="s">
@@ -23802,7 +23808,7 @@
     </row>
     <row r="858" spans="2:7" ht="15.75" customHeight="1">
       <c r="B858" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C858" s="4" t="s">
@@ -23823,7 +23829,7 @@
     </row>
     <row r="859" spans="2:7" ht="15.75" customHeight="1">
       <c r="B859" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C859" s="4" t="s">
@@ -23844,7 +23850,7 @@
     </row>
     <row r="860" spans="2:7" ht="15.75" customHeight="1">
       <c r="B860" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C860" s="4" t="s">
@@ -23865,7 +23871,7 @@
     </row>
     <row r="861" spans="2:7" ht="15.75" customHeight="1">
       <c r="B861" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C861" s="4" t="s">
@@ -23886,7 +23892,7 @@
     </row>
     <row r="862" spans="2:7" ht="15.75" customHeight="1">
       <c r="B862" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C862" s="4" t="s">
@@ -23907,7 +23913,7 @@
     </row>
     <row r="863" spans="2:7" ht="15.75" customHeight="1">
       <c r="B863" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C863" s="4" t="s">
@@ -23928,7 +23934,7 @@
     </row>
     <row r="864" spans="2:7" ht="15.75" customHeight="1">
       <c r="B864" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C864" s="4" t="s">
@@ -23949,7 +23955,7 @@
     </row>
     <row r="865" spans="2:7" ht="15.75" customHeight="1">
       <c r="B865" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C865" s="4" t="s">
@@ -23970,7 +23976,7 @@
     </row>
     <row r="866" spans="2:7" ht="15.75" customHeight="1">
       <c r="B866" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C866" s="4" t="s">
@@ -23991,7 +23997,7 @@
     </row>
     <row r="867" spans="2:7" ht="15.75" customHeight="1">
       <c r="B867" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C867" s="4" t="s">
@@ -24012,7 +24018,7 @@
     </row>
     <row r="868" spans="2:7" ht="15.75" customHeight="1">
       <c r="B868" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C868" s="4" t="s">
@@ -24033,7 +24039,7 @@
     </row>
     <row r="869" spans="2:7" ht="15.75" customHeight="1">
       <c r="B869" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C869" s="4" t="s">
@@ -24054,7 +24060,7 @@
     </row>
     <row r="870" spans="2:7" ht="15.75" customHeight="1">
       <c r="B870" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C870" s="4" t="s">
@@ -24075,7 +24081,7 @@
     </row>
     <row r="871" spans="2:7" ht="15.75" customHeight="1">
       <c r="B871" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C871" s="4" t="s">
@@ -24096,7 +24102,7 @@
     </row>
     <row r="872" spans="2:7" ht="15.75" customHeight="1">
       <c r="B872" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C872" s="4" t="s">
@@ -24117,7 +24123,7 @@
     </row>
     <row r="873" spans="2:7" ht="15.75" customHeight="1">
       <c r="B873" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C873" s="4" t="s">
@@ -24138,7 +24144,7 @@
     </row>
     <row r="874" spans="2:7" ht="15.75" customHeight="1">
       <c r="B874" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C874" s="4" t="s">
@@ -24159,7 +24165,7 @@
     </row>
     <row r="875" spans="2:7" ht="15.75" customHeight="1">
       <c r="B875" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C875" s="4" t="s">
@@ -24180,7 +24186,7 @@
     </row>
     <row r="876" spans="2:7" ht="15.75" customHeight="1">
       <c r="B876" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C876" s="4" t="s">
@@ -24201,7 +24207,7 @@
     </row>
     <row r="877" spans="2:7" ht="15.75" customHeight="1">
       <c r="B877" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C877" s="4" t="s">
@@ -24222,7 +24228,7 @@
     </row>
     <row r="878" spans="2:7" ht="15.75" customHeight="1">
       <c r="B878" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C878" s="4" t="s">
@@ -24243,7 +24249,7 @@
     </row>
     <row r="879" spans="2:7" ht="15.75" customHeight="1">
       <c r="B879" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C879" s="4" t="s">
@@ -24264,7 +24270,7 @@
     </row>
     <row r="880" spans="2:7" ht="15.75" customHeight="1">
       <c r="B880" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C880" s="4" t="s">
@@ -24285,7 +24291,7 @@
     </row>
     <row r="881" spans="2:7" ht="15.75" customHeight="1">
       <c r="B881" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C881" s="4" t="s">
@@ -24306,7 +24312,7 @@
     </row>
     <row r="882" spans="2:7" ht="15.75" customHeight="1">
       <c r="B882" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C882" s="4" t="s">
@@ -24327,7 +24333,7 @@
     </row>
     <row r="883" spans="2:7" ht="15.75" customHeight="1">
       <c r="B883" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C883" s="4" t="s">
@@ -24348,7 +24354,7 @@
     </row>
     <row r="884" spans="2:7" ht="15.75" customHeight="1">
       <c r="B884" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>46183</v>
       </c>
       <c r="C884" s="4" t="s">
@@ -24389,7 +24395,7 @@
     </row>
     <row r="886" spans="2:7" ht="15.75" customHeight="1">
       <c r="B886" s="6">
-        <f t="shared" ref="B886:B914" si="63">B885</f>
+        <f t="shared" ref="B886:B914" si="50">B885</f>
         <v>46184</v>
       </c>
       <c r="C886" s="4" t="s">
@@ -24410,7 +24416,7 @@
     </row>
     <row r="887" spans="2:7" ht="15.75" customHeight="1">
       <c r="B887" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C887" s="4" t="s">
@@ -24431,7 +24437,7 @@
     </row>
     <row r="888" spans="2:7" ht="15.75" customHeight="1">
       <c r="B888" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C888" s="4" t="s">
@@ -24452,7 +24458,7 @@
     </row>
     <row r="889" spans="2:7" ht="15.75" customHeight="1">
       <c r="B889" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C889" s="4" t="s">
@@ -24473,7 +24479,7 @@
     </row>
     <row r="890" spans="2:7" ht="15.75" customHeight="1">
       <c r="B890" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C890" s="4" t="s">
@@ -24494,7 +24500,7 @@
     </row>
     <row r="891" spans="2:7" ht="15.75" customHeight="1">
       <c r="B891" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C891" s="4" t="s">
@@ -24515,7 +24521,7 @@
     </row>
     <row r="892" spans="2:7" ht="15.75" customHeight="1">
       <c r="B892" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C892" s="4" t="s">
@@ -24536,7 +24542,7 @@
     </row>
     <row r="893" spans="2:7" ht="15.75" customHeight="1">
       <c r="B893" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C893" s="4" t="s">
@@ -24557,7 +24563,7 @@
     </row>
     <row r="894" spans="2:7" ht="15.75" customHeight="1">
       <c r="B894" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C894" s="4" t="s">
@@ -24578,7 +24584,7 @@
     </row>
     <row r="895" spans="2:7" ht="15.75" customHeight="1">
       <c r="B895" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C895" s="4" t="s">
@@ -24599,7 +24605,7 @@
     </row>
     <row r="896" spans="2:7" ht="15.75" customHeight="1">
       <c r="B896" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C896" s="4" t="s">
@@ -24620,7 +24626,7 @@
     </row>
     <row r="897" spans="2:7" ht="15.75" customHeight="1">
       <c r="B897" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C897" s="4" t="s">
@@ -24641,7 +24647,7 @@
     </row>
     <row r="898" spans="2:7" ht="15.75" customHeight="1">
       <c r="B898" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C898" s="4" t="s">
@@ -24662,7 +24668,7 @@
     </row>
     <row r="899" spans="2:7" ht="15.75" customHeight="1">
       <c r="B899" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C899" s="4" t="s">
@@ -24683,7 +24689,7 @@
     </row>
     <row r="900" spans="2:7" ht="15.75" customHeight="1">
       <c r="B900" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C900" s="4" t="s">
@@ -24704,7 +24710,7 @@
     </row>
     <row r="901" spans="2:7" ht="15.75" customHeight="1">
       <c r="B901" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C901" s="4" t="s">
@@ -24725,7 +24731,7 @@
     </row>
     <row r="902" spans="2:7" ht="15.75" customHeight="1">
       <c r="B902" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C902" s="4" t="s">
@@ -24746,7 +24752,7 @@
     </row>
     <row r="903" spans="2:7" ht="15.75" customHeight="1">
       <c r="B903" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C903" s="4" t="s">
@@ -24767,7 +24773,7 @@
     </row>
     <row r="904" spans="2:7" ht="15.75" customHeight="1">
       <c r="B904" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C904" s="4" t="s">
@@ -24788,7 +24794,7 @@
     </row>
     <row r="905" spans="2:7" ht="15.75" customHeight="1">
       <c r="B905" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C905" s="4" t="s">
@@ -24809,7 +24815,7 @@
     </row>
     <row r="906" spans="2:7" ht="15.75" customHeight="1">
       <c r="B906" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C906" s="4" t="s">
@@ -24830,7 +24836,7 @@
     </row>
     <row r="907" spans="2:7" ht="15.75" customHeight="1">
       <c r="B907" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C907" s="4" t="s">
@@ -24851,7 +24857,7 @@
     </row>
     <row r="908" spans="2:7" ht="15.75" customHeight="1">
       <c r="B908" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C908" s="4" t="s">
@@ -24872,7 +24878,7 @@
     </row>
     <row r="909" spans="2:7" ht="15.75" customHeight="1">
       <c r="B909" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C909" s="4" t="s">
@@ -24893,7 +24899,7 @@
     </row>
     <row r="910" spans="2:7" ht="15.75" customHeight="1">
       <c r="B910" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C910" s="4" t="s">
@@ -24914,7 +24920,7 @@
     </row>
     <row r="911" spans="2:7" ht="15.75" customHeight="1">
       <c r="B911" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C911" s="4" t="s">
@@ -24935,7 +24941,7 @@
     </row>
     <row r="912" spans="2:7" ht="15.75" customHeight="1">
       <c r="B912" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C912" s="4" t="s">
@@ -24956,7 +24962,7 @@
     </row>
     <row r="913" spans="2:7" ht="15.75" customHeight="1">
       <c r="B913" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C913" s="4" t="s">
@@ -24977,7 +24983,7 @@
     </row>
     <row r="914" spans="2:7" ht="15.75" customHeight="1">
       <c r="B914" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>46184</v>
       </c>
       <c r="C914" s="4" t="s">
@@ -25018,7 +25024,7 @@
     </row>
     <row r="916" spans="2:7" ht="15.75" customHeight="1">
       <c r="B916" s="6">
-        <f t="shared" ref="B916" si="64">B915</f>
+        <f>B915</f>
         <v>46185</v>
       </c>
       <c r="C916" s="4" t="s">
@@ -25059,7 +25065,7 @@
     </row>
     <row r="918" spans="2:7" ht="15.75" customHeight="1">
       <c r="B918" s="6">
-        <f t="shared" ref="B918" si="65">B917</f>
+        <f>B917</f>
         <v>46186</v>
       </c>
       <c r="C918" s="4" t="s">
@@ -25100,7 +25106,7 @@
     </row>
     <row r="920" spans="2:7" ht="15.75" customHeight="1">
       <c r="B920" s="6">
-        <f t="shared" ref="B920" si="66">B919</f>
+        <f>B919</f>
         <v>46189</v>
       </c>
       <c r="C920" s="4" t="s">
@@ -25141,7 +25147,7 @@
     </row>
     <row r="922" spans="2:7" ht="15.75" customHeight="1">
       <c r="B922" s="6">
-        <f t="shared" ref="B922" si="67">B921</f>
+        <f>B921</f>
         <v>46190</v>
       </c>
       <c r="C922" s="4" t="s">
@@ -25182,7 +25188,7 @@
     </row>
     <row r="924" spans="2:7" ht="15.75" customHeight="1">
       <c r="B924" s="6">
-        <f t="shared" ref="B924:B950" si="68">B923</f>
+        <f t="shared" ref="B924:B950" si="51">B923</f>
         <v>46191</v>
       </c>
       <c r="C924" s="7" t="s">
@@ -25203,7 +25209,7 @@
     </row>
     <row r="925" spans="2:7" ht="15.75" customHeight="1">
       <c r="B925" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C925" s="7" t="s">
@@ -25224,7 +25230,7 @@
     </row>
     <row r="926" spans="2:7" ht="15.75" customHeight="1">
       <c r="B926" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C926" s="7" t="s">
@@ -25245,7 +25251,7 @@
     </row>
     <row r="927" spans="2:7" ht="15.75" customHeight="1">
       <c r="B927" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C927" s="7" t="s">
@@ -25266,7 +25272,7 @@
     </row>
     <row r="928" spans="2:7" ht="15.75" customHeight="1">
       <c r="B928" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C928" s="7" t="s">
@@ -25287,7 +25293,7 @@
     </row>
     <row r="929" spans="2:7" ht="15.75" customHeight="1">
       <c r="B929" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C929" s="4" t="s">
@@ -25308,7 +25314,7 @@
     </row>
     <row r="930" spans="2:7" ht="15.75" customHeight="1">
       <c r="B930" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C930" s="7" t="s">
@@ -25329,7 +25335,7 @@
     </row>
     <row r="931" spans="2:7" ht="15.75" customHeight="1">
       <c r="B931" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C931" s="4" t="s">
@@ -25350,7 +25356,7 @@
     </row>
     <row r="932" spans="2:7" ht="15.75" customHeight="1">
       <c r="B932" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C932" s="4" t="s">
@@ -25371,7 +25377,7 @@
     </row>
     <row r="933" spans="2:7" ht="15.75" customHeight="1">
       <c r="B933" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C933" s="4" t="s">
@@ -25392,7 +25398,7 @@
     </row>
     <row r="934" spans="2:7" ht="15.75" customHeight="1">
       <c r="B934" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C934" s="4" t="s">
@@ -25413,7 +25419,7 @@
     </row>
     <row r="935" spans="2:7" ht="15.75" customHeight="1">
       <c r="B935" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C935" s="4" t="s">
@@ -25434,7 +25440,7 @@
     </row>
     <row r="936" spans="2:7" ht="15.75" customHeight="1">
       <c r="B936" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C936" s="4" t="s">
@@ -25455,7 +25461,7 @@
     </row>
     <row r="937" spans="2:7" ht="15.75" customHeight="1">
       <c r="B937" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C937" s="4" t="s">
@@ -25476,7 +25482,7 @@
     </row>
     <row r="938" spans="2:7" ht="15.75" customHeight="1">
       <c r="B938" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C938" s="4" t="s">
@@ -25497,7 +25503,7 @@
     </row>
     <row r="939" spans="2:7" ht="15.75" customHeight="1">
       <c r="B939" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C939" s="4" t="s">
@@ -25518,7 +25524,7 @@
     </row>
     <row r="940" spans="2:7" ht="15.75" customHeight="1">
       <c r="B940" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C940" s="4" t="s">
@@ -25539,7 +25545,7 @@
     </row>
     <row r="941" spans="2:7" ht="15.75" customHeight="1">
       <c r="B941" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C941" s="4" t="s">
@@ -25560,7 +25566,7 @@
     </row>
     <row r="942" spans="2:7" ht="15.75" customHeight="1">
       <c r="B942" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C942" s="4" t="s">
@@ -25581,7 +25587,7 @@
     </row>
     <row r="943" spans="2:7" ht="15.75" customHeight="1">
       <c r="B943" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C943" s="4" t="s">
@@ -25602,7 +25608,7 @@
     </row>
     <row r="944" spans="2:7" ht="15.75" customHeight="1">
       <c r="B944" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C944" s="4" t="s">
@@ -25623,7 +25629,7 @@
     </row>
     <row r="945" spans="2:7" ht="15.75" customHeight="1">
       <c r="B945" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C945" s="4" t="s">
@@ -25644,7 +25650,7 @@
     </row>
     <row r="946" spans="2:7" ht="15.75" customHeight="1">
       <c r="B946" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C946" s="4" t="s">
@@ -25665,7 +25671,7 @@
     </row>
     <row r="947" spans="2:7" ht="15.75" customHeight="1">
       <c r="B947" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C947" s="4" t="s">
@@ -25686,7 +25692,7 @@
     </row>
     <row r="948" spans="2:7" ht="15.75" customHeight="1">
       <c r="B948" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C948" s="4" t="s">
@@ -25707,7 +25713,7 @@
     </row>
     <row r="949" spans="2:7" ht="15.75" customHeight="1">
       <c r="B949" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C949" s="4" t="s">
@@ -25728,7 +25734,7 @@
     </row>
     <row r="950" spans="2:7" ht="15.75" customHeight="1">
       <c r="B950" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="51"/>
         <v>46191</v>
       </c>
       <c r="C950" s="4" t="s">
@@ -25789,7 +25795,7 @@
     </row>
     <row r="953" spans="2:7" ht="15.75" customHeight="1">
       <c r="B953" s="6">
-        <f t="shared" ref="B953" si="69">B952</f>
+        <f>B952</f>
         <v>46194</v>
       </c>
       <c r="C953" s="4" t="s">
@@ -25830,7 +25836,7 @@
     </row>
     <row r="955" spans="2:7" ht="15.75" customHeight="1">
       <c r="B955" s="6">
-        <f t="shared" ref="B955:B968" si="70">B954</f>
+        <f t="shared" ref="B955:B968" si="52">B954</f>
         <v>46195</v>
       </c>
       <c r="C955" s="4" t="s">
@@ -25851,7 +25857,7 @@
     </row>
     <row r="956" spans="2:7" ht="15.75" customHeight="1">
       <c r="B956" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C956" s="4" t="s">
@@ -25872,7 +25878,7 @@
     </row>
     <row r="957" spans="2:7" ht="15.75" customHeight="1">
       <c r="B957" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C957" s="4" t="s">
@@ -25893,7 +25899,7 @@
     </row>
     <row r="958" spans="2:7" ht="15.75" customHeight="1">
       <c r="B958" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C958" s="4" t="s">
@@ -25914,7 +25920,7 @@
     </row>
     <row r="959" spans="2:7" ht="15.75" customHeight="1">
       <c r="B959" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C959" s="4" t="s">
@@ -25935,7 +25941,7 @@
     </row>
     <row r="960" spans="2:7" ht="15.75" customHeight="1">
       <c r="B960" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C960" s="4" t="s">
@@ -25956,7 +25962,7 @@
     </row>
     <row r="961" spans="2:7" ht="15.75" customHeight="1">
       <c r="B961" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C961" s="4" t="s">
@@ -25977,7 +25983,7 @@
     </row>
     <row r="962" spans="2:7" ht="15.75" customHeight="1">
       <c r="B962" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C962" s="4" t="s">
@@ -25998,7 +26004,7 @@
     </row>
     <row r="963" spans="2:7" ht="15.75" customHeight="1">
       <c r="B963" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C963" s="4" t="s">
@@ -26019,7 +26025,7 @@
     </row>
     <row r="964" spans="2:7" ht="15.75" customHeight="1">
       <c r="B964" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C964" s="4" t="s">
@@ -26040,7 +26046,7 @@
     </row>
     <row r="965" spans="2:7" ht="15.75" customHeight="1">
       <c r="B965" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C965" s="4" t="s">
@@ -26061,7 +26067,7 @@
     </row>
     <row r="966" spans="2:7" ht="15.75" customHeight="1">
       <c r="B966" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C966" s="4" t="s">
@@ -26082,7 +26088,7 @@
     </row>
     <row r="967" spans="2:7" ht="15.75" customHeight="1">
       <c r="B967" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C967" s="4" t="s">
@@ -26103,7 +26109,7 @@
     </row>
     <row r="968" spans="2:7" ht="15.75" customHeight="1">
       <c r="B968" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="52"/>
         <v>46195</v>
       </c>
       <c r="C968" s="4" t="s">
@@ -26144,7 +26150,7 @@
     </row>
     <row r="970" spans="2:7" ht="15.75" customHeight="1">
       <c r="B970" s="6">
-        <f t="shared" ref="B970:B986" si="71">B969</f>
+        <f t="shared" ref="B970:B986" si="53">B969</f>
         <v>46196</v>
       </c>
       <c r="C970" s="4" t="s">
@@ -26165,7 +26171,7 @@
     </row>
     <row r="971" spans="2:7" ht="15.75" customHeight="1">
       <c r="B971" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C971" s="4" t="s">
@@ -26186,7 +26192,7 @@
     </row>
     <row r="972" spans="2:7" ht="15.75" customHeight="1">
       <c r="B972" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C972" s="4" t="s">
@@ -26207,7 +26213,7 @@
     </row>
     <row r="973" spans="2:7" ht="15.75" customHeight="1">
       <c r="B973" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C973" s="4" t="s">
@@ -26228,7 +26234,7 @@
     </row>
     <row r="974" spans="2:7" ht="15.75" customHeight="1">
       <c r="B974" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C974" s="4" t="s">
@@ -26249,7 +26255,7 @@
     </row>
     <row r="975" spans="2:7" ht="15.75" customHeight="1">
       <c r="B975" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C975" s="4" t="s">
@@ -26270,7 +26276,7 @@
     </row>
     <row r="976" spans="2:7" ht="15.75" customHeight="1">
       <c r="B976" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C976" s="4" t="s">
@@ -26291,7 +26297,7 @@
     </row>
     <row r="977" spans="2:7" ht="15.75" customHeight="1">
       <c r="B977" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C977" s="4" t="s">
@@ -26312,7 +26318,7 @@
     </row>
     <row r="978" spans="2:7" ht="15.75" customHeight="1">
       <c r="B978" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C978" s="4" t="s">
@@ -26333,7 +26339,7 @@
     </row>
     <row r="979" spans="2:7" ht="15.75" customHeight="1">
       <c r="B979" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C979" s="4" t="s">
@@ -26354,7 +26360,7 @@
     </row>
     <row r="980" spans="2:7" ht="15.75" customHeight="1">
       <c r="B980" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C980" s="4" t="s">
@@ -26375,7 +26381,7 @@
     </row>
     <row r="981" spans="2:7" ht="15.75" customHeight="1">
       <c r="B981" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C981" s="4" t="s">
@@ -26396,7 +26402,7 @@
     </row>
     <row r="982" spans="2:7" ht="15.75" customHeight="1">
       <c r="B982" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C982" s="4" t="s">
@@ -26417,7 +26423,7 @@
     </row>
     <row r="983" spans="2:7" ht="15.75" customHeight="1">
       <c r="B983" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C983" s="4" t="s">
@@ -26438,7 +26444,7 @@
     </row>
     <row r="984" spans="2:7" ht="15.75" customHeight="1">
       <c r="B984" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C984" s="4" t="s">
@@ -26459,7 +26465,7 @@
     </row>
     <row r="985" spans="2:7" ht="15.75" customHeight="1">
       <c r="B985" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C985" s="4" t="s">
@@ -26480,7 +26486,7 @@
     </row>
     <row r="986" spans="2:7" ht="15.75" customHeight="1">
       <c r="B986" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="53"/>
         <v>46196</v>
       </c>
       <c r="C986" s="4" t="s">
@@ -26561,7 +26567,7 @@
     </row>
     <row r="990" spans="2:7" ht="15.75" customHeight="1">
       <c r="B990" s="6">
-        <f t="shared" ref="B990:B992" si="72">B989</f>
+        <f>B989</f>
         <v>46199</v>
       </c>
       <c r="C990" s="4" t="s">
@@ -26582,7 +26588,7 @@
     </row>
     <row r="991" spans="2:7" ht="15.75" customHeight="1">
       <c r="B991" s="6">
-        <f t="shared" si="72"/>
+        <f>B990</f>
         <v>46199</v>
       </c>
       <c r="C991" s="4" t="s">
@@ -26603,7 +26609,7 @@
     </row>
     <row r="992" spans="2:7" ht="15" customHeight="1">
       <c r="B992" s="6">
-        <f t="shared" si="72"/>
+        <f>B991</f>
         <v>46199</v>
       </c>
       <c r="C992" s="4" t="s">
@@ -26644,7 +26650,7 @@
     </row>
     <row r="994" spans="2:7" ht="15" customHeight="1">
       <c r="B994" s="6">
-        <f t="shared" ref="B994:B998" si="73">B993</f>
+        <f>B993</f>
         <v>46201</v>
       </c>
       <c r="C994" s="4" t="s">
@@ -26665,7 +26671,7 @@
     </row>
     <row r="995" spans="2:7" ht="15" customHeight="1">
       <c r="B995" s="6">
-        <f t="shared" si="73"/>
+        <f>B994</f>
         <v>46201</v>
       </c>
       <c r="C995" s="4" t="s">
@@ -26686,7 +26692,7 @@
     </row>
     <row r="996" spans="2:7" ht="15" customHeight="1">
       <c r="B996" s="6">
-        <f t="shared" si="73"/>
+        <f>B995</f>
         <v>46201</v>
       </c>
       <c r="C996" s="4" t="s">
@@ -26707,7 +26713,7 @@
     </row>
     <row r="997" spans="2:7" ht="15" customHeight="1">
       <c r="B997" s="6">
-        <f t="shared" si="73"/>
+        <f>B996</f>
         <v>46201</v>
       </c>
       <c r="C997" s="4" t="s">
@@ -26728,7 +26734,7 @@
     </row>
     <row r="998" spans="2:7" ht="15" customHeight="1">
       <c r="B998" s="6">
-        <f t="shared" si="73"/>
+        <f>B997</f>
         <v>46201</v>
       </c>
       <c r="C998" s="4" t="s">
@@ -26769,7 +26775,7 @@
     </row>
     <row r="1000" spans="2:7" ht="15" customHeight="1">
       <c r="B1000" s="6">
-        <f t="shared" ref="B1000:B1003" si="74">B999</f>
+        <f>B999</f>
         <v>46202</v>
       </c>
       <c r="C1000" s="4" t="s">
@@ -26790,7 +26796,7 @@
     </row>
     <row r="1001" spans="2:7" ht="15" customHeight="1">
       <c r="B1001" s="6">
-        <f t="shared" si="74"/>
+        <f>B1000</f>
         <v>46202</v>
       </c>
       <c r="C1001" s="4" t="s">
@@ -26811,7 +26817,7 @@
     </row>
     <row r="1002" spans="2:7" ht="15" customHeight="1">
       <c r="B1002" s="6">
-        <f t="shared" si="74"/>
+        <f>B1001</f>
         <v>46202</v>
       </c>
       <c r="C1002" s="4" t="s">
@@ -26832,7 +26838,7 @@
     </row>
     <row r="1003" spans="2:7" ht="15" customHeight="1">
       <c r="B1003" s="6">
-        <f t="shared" si="74"/>
+        <f>B1002</f>
         <v>46202</v>
       </c>
       <c r="C1003" s="4" t="s">
@@ -26873,7 +26879,7 @@
     </row>
     <row r="1005" spans="2:7" ht="15" customHeight="1">
       <c r="B1005" s="6">
-        <f t="shared" ref="B1005:B1010" si="75">B1004</f>
+        <f t="shared" ref="B1005:B1010" si="54">B1004</f>
         <v>46203</v>
       </c>
       <c r="C1005" s="4" t="s">
@@ -26894,7 +26900,7 @@
     </row>
     <row r="1006" spans="2:7" ht="15" customHeight="1">
       <c r="B1006" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="54"/>
         <v>46203</v>
       </c>
       <c r="C1006" s="4" t="s">
@@ -26915,7 +26921,7 @@
     </row>
     <row r="1007" spans="2:7" ht="15" customHeight="1">
       <c r="B1007" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="54"/>
         <v>46203</v>
       </c>
       <c r="C1007" s="4" t="s">
@@ -26936,7 +26942,7 @@
     </row>
     <row r="1008" spans="2:7" ht="15" customHeight="1">
       <c r="B1008" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="54"/>
         <v>46203</v>
       </c>
       <c r="C1008" s="4" t="s">
@@ -26957,7 +26963,7 @@
     </row>
     <row r="1009" spans="2:7" ht="15" customHeight="1">
       <c r="B1009" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="54"/>
         <v>46203</v>
       </c>
       <c r="C1009" s="4" t="s">
@@ -26978,7 +26984,7 @@
     </row>
     <row r="1010" spans="2:7" ht="15" customHeight="1">
       <c r="B1010" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="54"/>
         <v>46203</v>
       </c>
       <c r="C1010" s="4" t="s">

--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -13,12 +13,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">plan1!$B$3:$G$1010</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5021" uniqueCount="1570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1571">
   <si>
     <t>Data</t>
   </si>
@@ -4721,13 +4720,16 @@
     <t>JUNHO</t>
   </si>
   <si>
-    <t xml:space="preserve">total de ocorrencia </t>
-  </si>
-  <si>
     <t>total de ocorrencia capturadas</t>
   </si>
   <si>
     <t>% de ocorrência capturadas</t>
+  </si>
+  <si>
+    <t>total de ocorrencia registradas</t>
+  </si>
+  <si>
+    <t>total de ocorrencia recebidas</t>
   </si>
 </sst>
 </file>
@@ -4919,7 +4921,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4972,6 +4974,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5353,7 +5356,7 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="28" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="I4" s="5">
         <v>2286</v>
@@ -5394,7 +5397,7 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="28" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="I5" s="5">
         <v>273</v>
@@ -5437,7 +5440,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="I6" s="29">
         <f>I5/I4</f>
@@ -5515,10 +5518,15 @@
         <v>19</v>
       </c>
       <c r="G8" s="8"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="I8" s="30" t="s">
+        <v>1564</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>1565</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>1566</v>
+      </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -5550,10 +5558,21 @@
       <c r="G9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="H9" s="28" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I9" s="34">
+        <f>100%-I10</f>
+        <v>0.88057742782152226</v>
+      </c>
+      <c r="J9" s="29">
+        <f>100%-J10</f>
+        <v>0.76622090143635457</v>
+      </c>
+      <c r="K9" s="29">
+        <f>100%-K10</f>
+        <v>0.86307938199254131</v>
+      </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -5586,10 +5605,18 @@
       <c r="G10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="H10" s="28" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I10" s="29">
+        <v>0.1194225721784777</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0.23377909856364537</v>
+      </c>
+      <c r="K10" s="29">
+        <v>0.13692061800745872</v>
+      </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>

--- a/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
+++ b/Planilhas/MONITORAMENTOS DE ALARMES COORDENACAO COR ABRIL-junho26 (consolidado).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6859" uniqueCount="2141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6861" uniqueCount="2142">
   <si>
     <t>Data</t>
   </si>
@@ -6444,6 +6444,9 @@
   </si>
   <si>
     <t>Unusual - Tixxi / CAM 83</t>
+  </si>
+  <si>
+    <t>JULHO</t>
   </si>
 </sst>
 </file>
@@ -6695,7 +6698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6778,6 +6781,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7095,6 +7099,9 @@
       <c r="L3" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="M3" s="4" t="s">
+        <v>2141</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -7132,6 +7139,9 @@
       </c>
       <c r="L4" s="10">
         <v>1877</v>
+      </c>
+      <c r="M4" s="54">
+        <v>2530</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -7175,7 +7185,9 @@
       <c r="L5" s="10">
         <v>257</v>
       </c>
-      <c r="M5" s="10"/>
+      <c r="M5" s="10">
+        <v>367</v>
+      </c>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -7286,7 +7298,9 @@
       <c r="L8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="10"/>
+      <c r="M8" s="4" t="s">
+        <v>2141</v>
+      </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
@@ -7333,7 +7347,10 @@
         <f>100%-L10</f>
         <v>0.86307938199254097</v>
       </c>
-      <c r="M9" s="10"/>
+      <c r="M9" s="19">
+        <f>100%-M10</f>
+        <v>0.85494071146245054</v>
+      </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
@@ -7378,7 +7395,10 @@
       <c r="L10" s="19">
         <v>0.136920618007459</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="19">
+        <f>M5/M4</f>
+        <v>0.1450592885375494</v>
+      </c>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
